--- a/Salary_Slip 2026-2027.xlsx
+++ b/Salary_Slip 2026-2027.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Hiran\Formats\PayslipApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70261E44-7E47-412A-A2DA-61F10E007AA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9BF7365-B352-49C4-BB53-E31D625B416A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="795" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Salary Silp" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="235">
   <si>
     <t>CAPITAL BRIDGE PRIVATE LIMITED</t>
   </si>
@@ -711,6 +711,27 @@
   </si>
   <si>
     <t>077-6672131</t>
+  </si>
+  <si>
+    <t>6/20</t>
+  </si>
+  <si>
+    <t>1/10</t>
+  </si>
+  <si>
+    <t>7/10</t>
+  </si>
+  <si>
+    <t>12/12</t>
+  </si>
+  <si>
+    <t>1/4</t>
+  </si>
+  <si>
+    <t>6/16</t>
+  </si>
+  <si>
+    <t>2/9</t>
   </si>
 </sst>
 </file>
@@ -1309,10 +1330,18 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="14" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1323,14 +1352,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="14" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1753,11 +1774,11 @@
       <c r="C8" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="73" t="str">
+      <c r="D8" s="68" t="str">
         <f>IFERROR(INDEX('Employee Master'!$C:$C,MATCH($A$6,'Employee Master'!$A:$A,0)),"")</f>
         <v>Assistant Accountant</v>
       </c>
-      <c r="E8" s="74"/>
+      <c r="E8" s="69"/>
     </row>
     <row r="9" spans="1:7" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="63" t="str">
@@ -1768,11 +1789,11 @@
       <c r="C9" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="73" t="str">
+      <c r="D9" s="68" t="str">
         <f>IFERROR(INDEX('Employee Master'!$D:$D,MATCH($A$6,'Employee Master'!$A:$A,0)),"")</f>
         <v xml:space="preserve">Finance &amp; Accounts </v>
       </c>
-      <c r="E9" s="74"/>
+      <c r="E9" s="69"/>
     </row>
     <row r="10" spans="1:7" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="str">
@@ -1930,7 +1951,7 @@
     <row r="22" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13"/>
       <c r="B22" s="14"/>
-      <c r="C22" s="70" t="s">
+      <c r="C22" s="74" t="s">
         <v>26</v>
       </c>
       <c r="D22" s="67"/>
@@ -2079,7 +2100,7 @@
     <row r="33" spans="1:7" s="62" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="13"/>
       <c r="B33" s="14"/>
-      <c r="C33" s="70" t="s">
+      <c r="C33" s="74" t="s">
         <v>36</v>
       </c>
       <c r="D33" s="67"/>
@@ -2099,7 +2120,7 @@
     <row r="35" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="19"/>
       <c r="B35" s="20"/>
-      <c r="C35" s="70" t="s">
+      <c r="C35" s="74" t="s">
         <v>37</v>
       </c>
       <c r="D35" s="67"/>
@@ -2119,7 +2140,7 @@
     <row r="37" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="17"/>
       <c r="B37" s="18"/>
-      <c r="C37" s="75" t="s">
+      <c r="C37" s="72" t="s">
         <v>38</v>
       </c>
       <c r="D37" s="46" t="s">
@@ -2135,7 +2156,7 @@
     <row r="38" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="17"/>
       <c r="B38" s="18"/>
-      <c r="C38" s="76"/>
+      <c r="C38" s="73"/>
       <c r="D38" s="46" t="s">
         <v>40</v>
       </c>
@@ -2171,26 +2192,26 @@
       <c r="E42"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="68" t="s">
+      <c r="A43" s="70" t="s">
         <v>41</v>
       </c>
-      <c r="B43" s="69"/>
+      <c r="B43" s="71"/>
       <c r="C43"/>
-      <c r="D43" s="68" t="s">
+      <c r="D43" s="70" t="s">
         <v>41</v>
       </c>
-      <c r="E43" s="69"/>
+      <c r="E43" s="71"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="77" t="s">
         <v>42</v>
       </c>
-      <c r="B44" s="69"/>
+      <c r="B44" s="71"/>
       <c r="C44"/>
       <c r="D44" s="77" t="s">
         <v>43</v>
       </c>
-      <c r="E44" s="69"/>
+      <c r="E44" s="71"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B45"/>
@@ -2202,22 +2223,34 @@
       <c r="A46" s="78" t="s">
         <v>44</v>
       </c>
-      <c r="B46" s="72"/>
-      <c r="C46" s="72"/>
-      <c r="D46" s="72"/>
-      <c r="E46" s="72"/>
+      <c r="B46" s="76"/>
+      <c r="C46" s="76"/>
+      <c r="D46" s="76"/>
+      <c r="E46" s="76"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="71" t="s">
+      <c r="A47" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="B47" s="72"/>
-      <c r="C47" s="72"/>
-      <c r="D47" s="72"/>
-      <c r="E47" s="72"/>
+      <c r="B47" s="76"/>
+      <c r="C47" s="76"/>
+      <c r="D47" s="76"/>
+      <c r="E47" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="A46:E46"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="D8:E8"/>
@@ -2233,19 +2266,7 @@
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="C33:D33"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="A46:E46"/>
     <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A19:C19"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="D6" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -9879,735 +9900,1338 @@
       <c r="A77" s="35">
         <v>46266</v>
       </c>
-      <c r="E77" s="43"/>
-      <c r="F77" s="43"/>
-      <c r="G77" s="43"/>
-      <c r="H77" s="43"/>
-      <c r="I77" s="43"/>
-      <c r="J77" s="43"/>
-      <c r="K77" s="43"/>
-      <c r="L77" s="43"/>
+      <c r="B77" t="s">
+        <v>60</v>
+      </c>
+      <c r="C77">
+        <v>5</v>
+      </c>
+      <c r="D77" t="s">
+        <v>61</v>
+      </c>
+      <c r="E77" s="43">
+        <v>61500</v>
+      </c>
+      <c r="F77" s="43">
+        <v>3500</v>
+      </c>
+      <c r="G77" s="43">
+        <v>53000</v>
+      </c>
+      <c r="H77" s="43">
+        <v>0</v>
+      </c>
+      <c r="I77" s="43">
+        <v>29000</v>
+      </c>
+      <c r="J77" s="43">
+        <v>30000</v>
+      </c>
+      <c r="K77" s="43">
+        <v>1000</v>
+      </c>
+      <c r="L77" s="43">
+        <v>0</v>
+      </c>
       <c r="M77" s="44">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>178000</v>
       </c>
       <c r="N77" s="44">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="O77" s="43"/>
-      <c r="P77" s="43"/>
-      <c r="Q77" s="43"/>
-      <c r="R77" s="43"/>
-      <c r="S77" s="43"/>
-      <c r="T77" s="43"/>
-      <c r="U77" s="43"/>
+        <v>5200</v>
+      </c>
+      <c r="O77" s="43">
+        <v>100000</v>
+      </c>
+      <c r="P77" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="43">
+        <v>9250</v>
+      </c>
+      <c r="R77" s="43">
+        <v>2775</v>
+      </c>
+      <c r="S77" s="43">
+        <v>0</v>
+      </c>
+      <c r="T77" s="43">
+        <v>0</v>
+      </c>
+      <c r="U77" s="43">
+        <v>1680</v>
+      </c>
       <c r="V77" s="44">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>118905</v>
       </c>
       <c r="W77" s="44">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>59095</v>
       </c>
       <c r="X77" s="44">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>7800</v>
       </c>
       <c r="Y77" s="44">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="Z77" s="50"/>
+        <v>1950</v>
+      </c>
+      <c r="Z77" s="50" t="s">
+        <v>228</v>
+      </c>
       <c r="AA77" s="47" t="str">
         <f t="shared" si="20"/>
-        <v>46266</v>
+        <v>46266R A A S Ranasinghe</v>
       </c>
     </row>
     <row r="78" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="35">
         <v>46266</v>
       </c>
-      <c r="E78" s="43"/>
-      <c r="F78" s="43"/>
-      <c r="G78" s="43"/>
-      <c r="H78" s="43"/>
-      <c r="I78" s="43"/>
-      <c r="J78" s="43"/>
-      <c r="K78" s="43"/>
-      <c r="L78" s="43"/>
+      <c r="B78" t="s">
+        <v>69</v>
+      </c>
+      <c r="C78">
+        <v>10</v>
+      </c>
+      <c r="D78" t="s">
+        <v>70</v>
+      </c>
+      <c r="E78" s="43">
+        <v>26500</v>
+      </c>
+      <c r="F78" s="43">
+        <v>3500</v>
+      </c>
+      <c r="G78" s="43">
+        <v>5000</v>
+      </c>
+      <c r="H78" s="43">
+        <v>0</v>
+      </c>
+      <c r="I78" s="43">
+        <v>7000</v>
+      </c>
+      <c r="J78" s="43">
+        <v>0</v>
+      </c>
+      <c r="K78" s="43">
+        <v>1000</v>
+      </c>
+      <c r="L78" s="43">
+        <v>1500</v>
+      </c>
       <c r="M78" s="44">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>44500</v>
       </c>
       <c r="N78" s="44">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="O78" s="43"/>
-      <c r="P78" s="43"/>
-      <c r="Q78" s="43"/>
-      <c r="R78" s="43"/>
-      <c r="S78" s="43"/>
-      <c r="T78" s="43"/>
-      <c r="U78" s="43"/>
+        <v>2400</v>
+      </c>
+      <c r="O78" s="43">
+        <v>0</v>
+      </c>
+      <c r="P78" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="43">
+        <v>7500</v>
+      </c>
+      <c r="R78" s="43">
+        <v>450</v>
+      </c>
+      <c r="S78" s="43">
+        <v>0</v>
+      </c>
+      <c r="T78" s="43">
+        <v>1500</v>
+      </c>
+      <c r="U78" s="43">
+        <v>0</v>
+      </c>
       <c r="V78" s="44">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>11850</v>
       </c>
       <c r="W78" s="44">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>32650</v>
       </c>
       <c r="X78" s="44">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="Y78" s="44">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="Z78" s="50"/>
+        <v>900</v>
+      </c>
+      <c r="Z78" s="50" t="s">
+        <v>202</v>
+      </c>
       <c r="AA78" s="47" t="str">
         <f t="shared" si="20"/>
-        <v>46266</v>
+        <v>46266P G U N Wimalasooriya</v>
       </c>
     </row>
     <row r="79" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="35">
         <v>46266</v>
       </c>
-      <c r="E79" s="43"/>
-      <c r="F79" s="43"/>
-      <c r="G79" s="43"/>
-      <c r="H79" s="43"/>
-      <c r="I79" s="43"/>
-      <c r="J79" s="43"/>
-      <c r="K79" s="43"/>
-      <c r="L79" s="43"/>
+      <c r="B79" t="s">
+        <v>77</v>
+      </c>
+      <c r="C79">
+        <v>16</v>
+      </c>
+      <c r="D79" t="s">
+        <v>78</v>
+      </c>
+      <c r="E79" s="43">
+        <v>41500</v>
+      </c>
+      <c r="F79" s="43">
+        <v>3500</v>
+      </c>
+      <c r="G79" s="43">
+        <v>17000</v>
+      </c>
+      <c r="H79" s="43">
+        <v>8000</v>
+      </c>
+      <c r="I79" s="43">
+        <v>28980</v>
+      </c>
+      <c r="J79" s="43">
+        <v>0</v>
+      </c>
+      <c r="K79" s="43">
+        <v>1000</v>
+      </c>
+      <c r="L79" s="43">
+        <v>3864</v>
+      </c>
       <c r="M79" s="44">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>103844</v>
       </c>
       <c r="N79" s="44">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="O79" s="43"/>
-      <c r="P79" s="43"/>
-      <c r="Q79" s="43"/>
-      <c r="R79" s="43"/>
-      <c r="S79" s="43"/>
-      <c r="T79" s="43"/>
-      <c r="U79" s="43"/>
+        <v>3600</v>
+      </c>
+      <c r="O79" s="43">
+        <v>15000</v>
+      </c>
+      <c r="P79" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="43">
+        <v>12500</v>
+      </c>
+      <c r="R79" s="43">
+        <v>3000</v>
+      </c>
+      <c r="S79" s="43">
+        <v>0</v>
+      </c>
+      <c r="T79" s="43">
+        <v>3864</v>
+      </c>
+      <c r="U79" s="43">
+        <v>0</v>
+      </c>
       <c r="V79" s="44">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>37964</v>
       </c>
       <c r="W79" s="44">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>65880</v>
       </c>
       <c r="X79" s="44">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="Y79" s="44">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="Z79" s="50"/>
+        <v>1350</v>
+      </c>
+      <c r="Z79" s="50" t="s">
+        <v>185</v>
+      </c>
       <c r="AA79" s="47" t="str">
         <f t="shared" si="20"/>
-        <v>46266</v>
+        <v>46266N M A G M Peiris</v>
       </c>
     </row>
     <row r="80" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="35">
         <v>46266</v>
       </c>
-      <c r="E80" s="43"/>
-      <c r="F80" s="43"/>
-      <c r="G80" s="43"/>
-      <c r="H80" s="43"/>
-      <c r="I80" s="43"/>
-      <c r="J80" s="43"/>
-      <c r="K80" s="43"/>
-      <c r="L80" s="43"/>
+      <c r="B80" t="s">
+        <v>85</v>
+      </c>
+      <c r="C80">
+        <v>17</v>
+      </c>
+      <c r="D80" t="s">
+        <v>86</v>
+      </c>
+      <c r="E80" s="43">
+        <v>31500</v>
+      </c>
+      <c r="F80" s="43">
+        <v>3500</v>
+      </c>
+      <c r="G80" s="43">
+        <v>7500</v>
+      </c>
+      <c r="H80" s="43">
+        <v>5000</v>
+      </c>
+      <c r="I80" s="43">
+        <v>28980</v>
+      </c>
+      <c r="J80" s="43">
+        <v>10000</v>
+      </c>
+      <c r="K80" s="43">
+        <v>1000</v>
+      </c>
+      <c r="L80" s="43">
+        <v>3260</v>
+      </c>
       <c r="M80" s="44">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>90740</v>
       </c>
       <c r="N80" s="44">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="O80" s="43"/>
-      <c r="P80" s="43"/>
-      <c r="Q80" s="43"/>
-      <c r="R80" s="43"/>
-      <c r="S80" s="43"/>
-      <c r="T80" s="43"/>
-      <c r="U80" s="43"/>
+        <v>2800</v>
+      </c>
+      <c r="O80" s="43">
+        <v>5000</v>
+      </c>
+      <c r="P80" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="43">
+        <v>10000</v>
+      </c>
+      <c r="R80" s="43">
+        <v>3000</v>
+      </c>
+      <c r="S80" s="43">
+        <v>0</v>
+      </c>
+      <c r="T80" s="43">
+        <v>3260</v>
+      </c>
+      <c r="U80" s="43">
+        <v>0</v>
+      </c>
       <c r="V80" s="44">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>24060</v>
       </c>
       <c r="W80" s="44">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>66680</v>
       </c>
       <c r="X80" s="44">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="Y80" s="44">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="Z80" s="50"/>
+        <v>1050</v>
+      </c>
+      <c r="Z80" s="50" t="s">
+        <v>229</v>
+      </c>
       <c r="AA80" s="47" t="str">
         <f t="shared" si="20"/>
-        <v>46266</v>
+        <v>46266K R T Hemantha</v>
       </c>
     </row>
     <row r="81" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="35">
         <v>46266</v>
       </c>
-      <c r="E81" s="43"/>
-      <c r="F81" s="43"/>
-      <c r="G81" s="43"/>
-      <c r="H81" s="43"/>
-      <c r="I81" s="43"/>
-      <c r="J81" s="43"/>
-      <c r="K81" s="43"/>
-      <c r="L81" s="43"/>
+      <c r="B81" t="s">
+        <v>92</v>
+      </c>
+      <c r="C81">
+        <v>18</v>
+      </c>
+      <c r="D81" t="s">
+        <v>93</v>
+      </c>
+      <c r="E81" s="43">
+        <v>56500</v>
+      </c>
+      <c r="F81" s="43">
+        <v>3500</v>
+      </c>
+      <c r="G81" s="43">
+        <v>26000</v>
+      </c>
+      <c r="H81" s="43">
+        <v>0</v>
+      </c>
+      <c r="I81" s="43">
+        <v>13000</v>
+      </c>
+      <c r="J81" s="43">
+        <v>0</v>
+      </c>
+      <c r="K81" s="43">
+        <v>1000</v>
+      </c>
+      <c r="L81" s="43">
+        <v>1500</v>
+      </c>
       <c r="M81" s="44">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>101500</v>
       </c>
       <c r="N81" s="44">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="O81" s="43"/>
-      <c r="P81" s="43"/>
-      <c r="Q81" s="43"/>
-      <c r="R81" s="43"/>
-      <c r="S81" s="43"/>
-      <c r="T81" s="43"/>
-      <c r="U81" s="43"/>
+        <v>4800</v>
+      </c>
+      <c r="O81" s="43">
+        <v>0</v>
+      </c>
+      <c r="P81" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="43">
+        <v>10000</v>
+      </c>
+      <c r="R81" s="43">
+        <v>1200</v>
+      </c>
+      <c r="S81" s="43">
+        <v>0</v>
+      </c>
+      <c r="T81" s="43">
+        <v>1500</v>
+      </c>
+      <c r="U81" s="43">
+        <v>0</v>
+      </c>
       <c r="V81" s="44">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>17500</v>
       </c>
       <c r="W81" s="44">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>84000</v>
       </c>
       <c r="X81" s="44">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>7200</v>
       </c>
       <c r="Y81" s="44">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="Z81" s="50"/>
+        <v>1800</v>
+      </c>
+      <c r="Z81" s="50" t="s">
+        <v>230</v>
+      </c>
       <c r="AA81" s="47" t="str">
         <f t="shared" si="20"/>
-        <v>46266</v>
+        <v>46266W M H M Weerasinghe</v>
       </c>
     </row>
     <row r="82" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="35">
         <v>46266</v>
       </c>
-      <c r="E82" s="43"/>
-      <c r="F82" s="43"/>
-      <c r="G82" s="43"/>
-      <c r="H82" s="43"/>
-      <c r="I82" s="43"/>
-      <c r="J82" s="43"/>
-      <c r="K82" s="43"/>
-      <c r="L82" s="43"/>
+      <c r="B82" t="s">
+        <v>99</v>
+      </c>
+      <c r="C82">
+        <v>19</v>
+      </c>
+      <c r="D82" t="s">
+        <v>86</v>
+      </c>
+      <c r="E82" s="43">
+        <v>36500</v>
+      </c>
+      <c r="F82" s="43">
+        <v>3500</v>
+      </c>
+      <c r="G82" s="43">
+        <v>7500</v>
+      </c>
+      <c r="H82" s="43">
+        <v>5000</v>
+      </c>
+      <c r="I82" s="43">
+        <v>28980</v>
+      </c>
+      <c r="J82" s="43">
+        <v>10000</v>
+      </c>
+      <c r="K82" s="43">
+        <v>1000</v>
+      </c>
+      <c r="L82" s="43">
+        <v>8000</v>
+      </c>
       <c r="M82" s="44">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>100480</v>
       </c>
       <c r="N82" s="44">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="O82" s="43"/>
-      <c r="P82" s="43"/>
-      <c r="Q82" s="43"/>
-      <c r="R82" s="43"/>
+        <v>3200</v>
+      </c>
+      <c r="O82" s="43">
+        <v>0</v>
+      </c>
+      <c r="P82" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="43">
+        <v>8333.33</v>
+      </c>
+      <c r="R82" s="43">
+        <v>249.9999</v>
+      </c>
       <c r="S82" s="43"/>
-      <c r="T82" s="43"/>
-      <c r="U82" s="43"/>
+      <c r="T82" s="43">
+        <v>8000</v>
+      </c>
+      <c r="U82" s="43">
+        <v>0</v>
+      </c>
       <c r="V82" s="44">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>19783.329900000001</v>
       </c>
       <c r="W82" s="44">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>80696.670100000003</v>
       </c>
       <c r="X82" s="44">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="Y82" s="44">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="Z82" s="50"/>
+        <v>1200</v>
+      </c>
+      <c r="Z82" s="50" t="s">
+        <v>231</v>
+      </c>
       <c r="AA82" s="47" t="str">
         <f t="shared" si="20"/>
-        <v>46266</v>
+        <v>46266R W D S Wijerathna</v>
       </c>
     </row>
     <row r="83" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="35">
         <v>46266</v>
       </c>
-      <c r="E83" s="43"/>
-      <c r="F83" s="43"/>
-      <c r="G83" s="43"/>
-      <c r="H83" s="43"/>
-      <c r="I83" s="43"/>
-      <c r="J83" s="43"/>
-      <c r="K83" s="43"/>
-      <c r="L83" s="43"/>
+      <c r="B83" t="s">
+        <v>103</v>
+      </c>
+      <c r="C83">
+        <v>21</v>
+      </c>
+      <c r="D83" t="s">
+        <v>104</v>
+      </c>
+      <c r="E83" s="43">
+        <v>26500</v>
+      </c>
+      <c r="F83" s="43">
+        <v>3500</v>
+      </c>
+      <c r="G83" s="43">
+        <v>0</v>
+      </c>
+      <c r="H83" s="43">
+        <v>0</v>
+      </c>
+      <c r="I83" s="43">
+        <v>5000</v>
+      </c>
+      <c r="J83" s="43">
+        <v>0</v>
+      </c>
+      <c r="K83" s="43">
+        <v>1000</v>
+      </c>
+      <c r="L83" s="43">
+        <v>1500</v>
+      </c>
       <c r="M83" s="44">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>37500</v>
       </c>
       <c r="N83" s="44">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="O83" s="43"/>
-      <c r="P83" s="43"/>
-      <c r="Q83" s="43"/>
-      <c r="R83" s="43"/>
-      <c r="S83" s="43"/>
-      <c r="T83" s="43"/>
-      <c r="U83" s="43"/>
+        <v>2400</v>
+      </c>
+      <c r="O83" s="43">
+        <v>2000</v>
+      </c>
+      <c r="P83" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="43">
+        <v>6250</v>
+      </c>
+      <c r="R83" s="43">
+        <v>750</v>
+      </c>
+      <c r="S83" s="43">
+        <v>0</v>
+      </c>
+      <c r="T83" s="43">
+        <v>1500</v>
+      </c>
+      <c r="U83" s="43">
+        <v>0</v>
+      </c>
       <c r="V83" s="44">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>12900</v>
       </c>
       <c r="W83" s="44">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>24600</v>
       </c>
       <c r="X83" s="44">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="Y83" s="44">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="Z83" s="50"/>
+        <v>900</v>
+      </c>
+      <c r="Z83" s="50" t="s">
+        <v>232</v>
+      </c>
       <c r="AA83" s="47" t="str">
         <f t="shared" si="20"/>
-        <v>46266</v>
+        <v>46266S Wathmi Sankalpana</v>
       </c>
     </row>
     <row r="84" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="35">
         <v>46266</v>
       </c>
-      <c r="E84" s="43"/>
-      <c r="F84" s="43"/>
-      <c r="G84" s="43"/>
-      <c r="H84" s="43"/>
-      <c r="I84" s="43"/>
-      <c r="J84" s="43"/>
-      <c r="K84" s="43"/>
-      <c r="L84" s="43"/>
+      <c r="B84" t="s">
+        <v>110</v>
+      </c>
+      <c r="C84">
+        <v>22</v>
+      </c>
+      <c r="D84" t="s">
+        <v>111</v>
+      </c>
+      <c r="E84" s="43">
+        <v>26500</v>
+      </c>
+      <c r="F84" s="43">
+        <v>3500</v>
+      </c>
+      <c r="G84" s="43">
+        <v>5000</v>
+      </c>
+      <c r="H84" s="43">
+        <v>2760</v>
+      </c>
+      <c r="I84" s="43">
+        <v>26910</v>
+      </c>
+      <c r="J84" s="43">
+        <v>10000</v>
+      </c>
+      <c r="K84" s="43">
+        <v>1000</v>
+      </c>
+      <c r="L84" s="43">
+        <v>6840</v>
+      </c>
       <c r="M84" s="44">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>82510</v>
       </c>
       <c r="N84" s="44">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="O84" s="43"/>
-      <c r="P84" s="43"/>
-      <c r="Q84" s="43"/>
-      <c r="R84" s="43"/>
-      <c r="S84" s="43"/>
-      <c r="T84" s="43"/>
-      <c r="U84" s="43"/>
+        <v>2400</v>
+      </c>
+      <c r="O84" s="43">
+        <v>0</v>
+      </c>
+      <c r="P84" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="43">
+        <v>5000</v>
+      </c>
+      <c r="R84" s="43">
+        <v>1650</v>
+      </c>
+      <c r="S84" s="43">
+        <v>0</v>
+      </c>
+      <c r="T84" s="43">
+        <v>6840</v>
+      </c>
+      <c r="U84" s="43">
+        <v>0</v>
+      </c>
       <c r="V84" s="44">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>15890</v>
       </c>
       <c r="W84" s="44">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>66620</v>
       </c>
       <c r="X84" s="44">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="Y84" s="44">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="Z84" s="50"/>
+        <v>900</v>
+      </c>
+      <c r="Z84" s="50" t="s">
+        <v>233</v>
+      </c>
       <c r="AA84" s="47" t="str">
         <f t="shared" si="20"/>
-        <v>46266</v>
+        <v>46266E M P P W O R K Jayawardana</v>
       </c>
     </row>
     <row r="85" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="35">
         <v>46266</v>
       </c>
-      <c r="E85" s="43"/>
-      <c r="F85" s="43"/>
-      <c r="G85" s="43"/>
-      <c r="H85" s="43"/>
-      <c r="I85" s="43"/>
-      <c r="J85" s="43"/>
-      <c r="K85" s="43"/>
-      <c r="L85" s="43"/>
+      <c r="B85" t="s">
+        <v>116</v>
+      </c>
+      <c r="C85">
+        <v>23</v>
+      </c>
+      <c r="D85" t="s">
+        <v>111</v>
+      </c>
+      <c r="E85" s="43">
+        <v>26500</v>
+      </c>
+      <c r="F85" s="43">
+        <v>3500</v>
+      </c>
+      <c r="G85" s="43">
+        <v>7000</v>
+      </c>
+      <c r="H85" s="43">
+        <v>5000</v>
+      </c>
+      <c r="I85" s="43">
+        <v>28980</v>
+      </c>
+      <c r="J85" s="43">
+        <v>0</v>
+      </c>
+      <c r="K85" s="43">
+        <v>1000</v>
+      </c>
+      <c r="L85" s="43">
+        <v>3840</v>
+      </c>
       <c r="M85" s="44">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>75820</v>
       </c>
       <c r="N85" s="44">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="O85" s="43"/>
-      <c r="P85" s="43"/>
-      <c r="Q85" s="43"/>
-      <c r="R85" s="43"/>
-      <c r="S85" s="43"/>
-      <c r="T85" s="43"/>
-      <c r="U85" s="43"/>
+        <v>2400</v>
+      </c>
+      <c r="O85" s="43">
+        <v>5000</v>
+      </c>
+      <c r="P85" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="43">
+        <v>0</v>
+      </c>
+      <c r="R85" s="43">
+        <v>0</v>
+      </c>
+      <c r="S85" s="43">
+        <v>0</v>
+      </c>
+      <c r="T85" s="43">
+        <v>3840</v>
+      </c>
+      <c r="U85" s="43">
+        <v>0</v>
+      </c>
       <c r="V85" s="44">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>11240</v>
       </c>
       <c r="W85" s="44">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>64580</v>
       </c>
       <c r="X85" s="44">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="Y85" s="44">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="Z85" s="50"/>
       <c r="AA85" s="47" t="str">
         <f t="shared" si="20"/>
-        <v>46266</v>
+        <v>46266T M R L B Thennakoon</v>
       </c>
     </row>
     <row r="86" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="35">
         <v>46266</v>
       </c>
-      <c r="E86" s="43"/>
-      <c r="F86" s="43"/>
-      <c r="G86" s="43"/>
-      <c r="H86" s="43"/>
-      <c r="I86" s="43"/>
-      <c r="J86" s="43"/>
-      <c r="K86" s="43"/>
-      <c r="L86" s="43"/>
+      <c r="B86" t="s">
+        <v>121</v>
+      </c>
+      <c r="C86">
+        <v>24</v>
+      </c>
+      <c r="D86" t="s">
+        <v>86</v>
+      </c>
+      <c r="E86" s="43">
+        <v>31500</v>
+      </c>
+      <c r="F86" s="43">
+        <v>3500</v>
+      </c>
+      <c r="G86" s="43">
+        <v>7500</v>
+      </c>
+      <c r="H86" s="43">
+        <v>5000</v>
+      </c>
+      <c r="I86" s="43">
+        <v>26910</v>
+      </c>
+      <c r="J86" s="43">
+        <v>0</v>
+      </c>
+      <c r="K86" s="43">
+        <v>1000</v>
+      </c>
+      <c r="L86" s="43">
+        <v>6520</v>
+      </c>
       <c r="M86" s="44">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>81930</v>
       </c>
       <c r="N86" s="44">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="O86" s="43"/>
-      <c r="P86" s="43"/>
-      <c r="Q86" s="43"/>
-      <c r="R86" s="43"/>
-      <c r="S86" s="43"/>
-      <c r="T86" s="43"/>
-      <c r="U86" s="43"/>
+        <v>2800</v>
+      </c>
+      <c r="O86" s="43">
+        <v>0</v>
+      </c>
+      <c r="P86" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="43">
+        <v>0</v>
+      </c>
+      <c r="R86" s="43">
+        <v>0</v>
+      </c>
+      <c r="S86" s="43">
+        <v>0</v>
+      </c>
+      <c r="T86" s="43">
+        <v>6520</v>
+      </c>
+      <c r="U86" s="43">
+        <v>0</v>
+      </c>
       <c r="V86" s="44">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>9320</v>
       </c>
       <c r="W86" s="44">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>72610</v>
       </c>
       <c r="X86" s="44">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="Y86" s="44">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>1050</v>
       </c>
       <c r="Z86" s="50"/>
       <c r="AA86" s="47" t="str">
         <f t="shared" si="20"/>
-        <v>46266</v>
+        <v>46266W K Senaverathna</v>
       </c>
     </row>
     <row r="87" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="35">
         <v>46266</v>
       </c>
-      <c r="E87" s="43"/>
-      <c r="F87" s="43"/>
-      <c r="G87" s="43"/>
-      <c r="H87" s="43"/>
-      <c r="I87" s="43"/>
-      <c r="J87" s="43"/>
-      <c r="K87" s="43"/>
-      <c r="L87" s="43"/>
+      <c r="B87" t="s">
+        <v>127</v>
+      </c>
+      <c r="C87">
+        <v>25</v>
+      </c>
+      <c r="D87" t="s">
+        <v>86</v>
+      </c>
+      <c r="E87" s="43">
+        <v>36500</v>
+      </c>
+      <c r="F87" s="43">
+        <v>3500</v>
+      </c>
+      <c r="G87" s="43">
+        <v>5000</v>
+      </c>
+      <c r="H87" s="43">
+        <v>5000</v>
+      </c>
+      <c r="I87" s="43">
+        <v>28980</v>
+      </c>
+      <c r="J87" s="43">
+        <v>10000</v>
+      </c>
+      <c r="K87" s="43">
+        <v>1000</v>
+      </c>
+      <c r="L87" s="43">
+        <v>3220</v>
+      </c>
       <c r="M87" s="44">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>93200</v>
       </c>
       <c r="N87" s="44">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="O87" s="43"/>
-      <c r="P87" s="43"/>
-      <c r="Q87" s="43"/>
-      <c r="R87" s="43"/>
-      <c r="S87" s="43"/>
-      <c r="T87" s="43"/>
-      <c r="U87" s="43"/>
+        <v>3200</v>
+      </c>
+      <c r="O87" s="43">
+        <v>15000</v>
+      </c>
+      <c r="P87" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="43">
+        <v>10000</v>
+      </c>
+      <c r="R87" s="43">
+        <v>3000</v>
+      </c>
+      <c r="S87" s="43">
+        <v>0</v>
+      </c>
+      <c r="T87" s="43">
+        <v>3220</v>
+      </c>
+      <c r="U87" s="43">
+        <v>0</v>
+      </c>
       <c r="V87" s="44">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>34420</v>
       </c>
       <c r="W87" s="44">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>58780</v>
       </c>
       <c r="X87" s="44">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="Y87" s="44">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="Z87" s="50"/>
+        <v>1200</v>
+      </c>
+      <c r="Z87" s="50" t="s">
+        <v>229</v>
+      </c>
       <c r="AA87" s="47" t="str">
         <f t="shared" si="20"/>
-        <v>46266</v>
+        <v>46266D R G S L Ranaweera</v>
       </c>
     </row>
     <row r="88" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="35">
         <v>46266</v>
       </c>
-      <c r="E88" s="43"/>
-      <c r="F88" s="43"/>
-      <c r="G88" s="43"/>
-      <c r="H88" s="43"/>
-      <c r="I88" s="43"/>
-      <c r="J88" s="43"/>
-      <c r="K88" s="43"/>
-      <c r="L88" s="43"/>
+      <c r="B88" t="s">
+        <v>132</v>
+      </c>
+      <c r="C88">
+        <v>26</v>
+      </c>
+      <c r="D88" t="s">
+        <v>104</v>
+      </c>
+      <c r="E88" s="43">
+        <v>26500</v>
+      </c>
+      <c r="F88" s="43">
+        <v>3500</v>
+      </c>
+      <c r="G88" s="43">
+        <v>0</v>
+      </c>
+      <c r="H88" s="43">
+        <v>0</v>
+      </c>
+      <c r="I88" s="43">
+        <v>0</v>
+      </c>
+      <c r="J88" s="43">
+        <v>0</v>
+      </c>
+      <c r="K88" s="43">
+        <v>1000</v>
+      </c>
+      <c r="L88" s="43">
+        <v>1500</v>
+      </c>
       <c r="M88" s="44">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>32500</v>
       </c>
       <c r="N88" s="44">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="O88" s="43"/>
-      <c r="P88" s="43"/>
-      <c r="Q88" s="43"/>
-      <c r="R88" s="43"/>
-      <c r="S88" s="43"/>
-      <c r="T88" s="43"/>
-      <c r="U88" s="43"/>
+        <v>2400</v>
+      </c>
+      <c r="O88" s="43">
+        <v>0</v>
+      </c>
+      <c r="P88" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="43">
+        <v>0</v>
+      </c>
+      <c r="R88" s="43">
+        <v>0</v>
+      </c>
+      <c r="S88" s="43">
+        <v>0</v>
+      </c>
+      <c r="T88" s="43">
+        <v>1500</v>
+      </c>
+      <c r="U88" s="43">
+        <v>0</v>
+      </c>
       <c r="V88" s="44">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3900</v>
       </c>
       <c r="W88" s="44">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>28600</v>
       </c>
       <c r="X88" s="44">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="Y88" s="44">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="Z88" s="50"/>
       <c r="AA88" s="47" t="str">
         <f t="shared" si="20"/>
-        <v>46266</v>
+        <v>46266W A A Heshani Bandara</v>
       </c>
     </row>
     <row r="89" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="35">
         <v>46266</v>
       </c>
-      <c r="E89" s="43"/>
-      <c r="F89" s="43"/>
-      <c r="G89" s="43"/>
-      <c r="H89" s="43"/>
-      <c r="I89" s="43"/>
-      <c r="J89" s="43"/>
-      <c r="K89" s="43"/>
-      <c r="L89" s="43"/>
+      <c r="B89" t="s">
+        <v>8</v>
+      </c>
+      <c r="C89">
+        <v>27</v>
+      </c>
+      <c r="D89" t="s">
+        <v>111</v>
+      </c>
+      <c r="E89" s="43">
+        <v>26500</v>
+      </c>
+      <c r="F89" s="43">
+        <v>3500</v>
+      </c>
+      <c r="G89" s="43">
+        <v>2500</v>
+      </c>
+      <c r="H89" s="43">
+        <v>2500</v>
+      </c>
+      <c r="I89" s="43">
+        <v>24840</v>
+      </c>
+      <c r="J89" s="43">
+        <v>10000</v>
+      </c>
+      <c r="K89" s="43">
+        <v>1000</v>
+      </c>
+      <c r="L89" s="43">
+        <v>8440</v>
+      </c>
       <c r="M89" s="44">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>79280</v>
       </c>
       <c r="N89" s="44">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="O89" s="43"/>
-      <c r="P89" s="43"/>
-      <c r="Q89" s="43"/>
-      <c r="R89" s="43"/>
-      <c r="S89" s="43"/>
-      <c r="T89" s="43"/>
-      <c r="U89" s="43"/>
+        <v>2400</v>
+      </c>
+      <c r="O89" s="43">
+        <v>0</v>
+      </c>
+      <c r="P89" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="43">
+        <v>10000</v>
+      </c>
+      <c r="R89" s="43">
+        <v>2400</v>
+      </c>
+      <c r="S89" s="43">
+        <v>0</v>
+      </c>
+      <c r="T89" s="43">
+        <v>8440</v>
+      </c>
+      <c r="U89" s="43">
+        <v>0</v>
+      </c>
       <c r="V89" s="44">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>23240</v>
       </c>
       <c r="W89" s="44">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>56040</v>
       </c>
       <c r="X89" s="44">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="Y89" s="44">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="Z89" s="50"/>
+        <v>900</v>
+      </c>
+      <c r="Z89" s="50" t="s">
+        <v>234</v>
+      </c>
       <c r="AA89" s="47" t="str">
         <f t="shared" si="20"/>
-        <v>46266</v>
+        <v>46266D M T S Disanayake</v>
       </c>
     </row>
     <row r="90" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="35">
         <v>46266</v>
       </c>
-      <c r="E90" s="43"/>
-      <c r="F90" s="43"/>
-      <c r="G90" s="43"/>
-      <c r="H90" s="43"/>
-      <c r="I90" s="43"/>
-      <c r="J90" s="43"/>
-      <c r="K90" s="43"/>
-      <c r="L90" s="43"/>
+      <c r="B90" t="s">
+        <v>141</v>
+      </c>
+      <c r="C90">
+        <v>28</v>
+      </c>
+      <c r="D90" t="s">
+        <v>86</v>
+      </c>
+      <c r="E90" s="43">
+        <v>36500</v>
+      </c>
+      <c r="F90" s="43">
+        <v>3500</v>
+      </c>
+      <c r="G90" s="43">
+        <v>10000</v>
+      </c>
+      <c r="H90" s="43">
+        <v>5000</v>
+      </c>
+      <c r="I90" s="43">
+        <v>26910</v>
+      </c>
+      <c r="J90" s="43">
+        <v>10000</v>
+      </c>
+      <c r="K90" s="43">
+        <v>1000</v>
+      </c>
+      <c r="L90" s="43">
+        <v>6720</v>
+      </c>
       <c r="M90" s="44">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>99630</v>
       </c>
       <c r="N90" s="44">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="O90" s="43"/>
-      <c r="P90" s="43"/>
-      <c r="Q90" s="43"/>
-      <c r="R90" s="43"/>
-      <c r="S90" s="43"/>
-      <c r="T90" s="43"/>
-      <c r="U90" s="43"/>
+        <v>3200</v>
+      </c>
+      <c r="O90" s="43">
+        <v>15000</v>
+      </c>
+      <c r="P90" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="43">
+        <v>0</v>
+      </c>
+      <c r="R90" s="43">
+        <v>0</v>
+      </c>
+      <c r="S90" s="43">
+        <v>0</v>
+      </c>
+      <c r="T90" s="43">
+        <v>6720</v>
+      </c>
+      <c r="U90" s="43">
+        <v>0</v>
+      </c>
       <c r="V90" s="44">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>24920</v>
       </c>
       <c r="W90" s="44">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>74710</v>
       </c>
       <c r="X90" s="44">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="Y90" s="44">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="Z90" s="50"/>
       <c r="AA90" s="47" t="str">
         <f t="shared" si="20"/>
-        <v>46266</v>
+        <v>46266P L D B Wijewardhna</v>
       </c>
     </row>
     <row r="91" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="35">
         <v>46266</v>
       </c>
-      <c r="E91" s="43"/>
-      <c r="F91" s="43"/>
-      <c r="G91" s="43"/>
-      <c r="H91" s="43"/>
-      <c r="I91" s="43"/>
-      <c r="J91" s="43"/>
-      <c r="K91" s="43"/>
-      <c r="L91" s="43"/>
+      <c r="B91" t="s">
+        <v>146</v>
+      </c>
+      <c r="C91">
+        <v>29</v>
+      </c>
+      <c r="D91" t="s">
+        <v>111</v>
+      </c>
+      <c r="E91" s="43">
+        <v>26500</v>
+      </c>
+      <c r="F91" s="43">
+        <v>3500</v>
+      </c>
+      <c r="G91" s="43">
+        <v>5000</v>
+      </c>
+      <c r="H91" s="43">
+        <v>5000</v>
+      </c>
+      <c r="I91" s="43">
+        <v>18630</v>
+      </c>
+      <c r="J91" s="43">
+        <v>0</v>
+      </c>
+      <c r="K91" s="43">
+        <v>1000</v>
+      </c>
+      <c r="L91" s="43">
+        <v>1500</v>
+      </c>
       <c r="M91" s="44">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>61130</v>
       </c>
       <c r="N91" s="44">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="O91" s="43"/>
-      <c r="P91" s="43"/>
-      <c r="Q91" s="43"/>
-      <c r="R91" s="43"/>
-      <c r="S91" s="43"/>
-      <c r="T91" s="43"/>
-      <c r="U91" s="43"/>
+        <v>2400</v>
+      </c>
+      <c r="O91" s="43">
+        <v>12000</v>
+      </c>
+      <c r="P91" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="43">
+        <v>0</v>
+      </c>
+      <c r="R91" s="43">
+        <v>0</v>
+      </c>
+      <c r="S91" s="43">
+        <v>0</v>
+      </c>
+      <c r="T91" s="43">
+        <v>1500</v>
+      </c>
+      <c r="U91" s="43">
+        <v>0</v>
+      </c>
       <c r="V91" s="44">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>15900</v>
       </c>
       <c r="W91" s="44">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>45230</v>
       </c>
       <c r="X91" s="44">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="Y91" s="44">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="Z91" s="50"/>
       <c r="AA91" s="47" t="str">
         <f t="shared" si="20"/>
-        <v>46266</v>
+        <v>46266N G L D Supunsiri</v>
       </c>
     </row>
     <row r="92" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">

--- a/Salary_Slip 2026-2027.xlsx
+++ b/Salary_Slip 2026-2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Hiran\Formats\PayslipApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9BF7365-B352-49C4-BB53-E31D625B416A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F53E9C55-6015-413C-B20A-2E578126F471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="795" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9942,7 +9942,7 @@
         <v>5200</v>
       </c>
       <c r="O77" s="43">
-        <v>100000</v>
+        <v>102500</v>
       </c>
       <c r="P77" s="43">
         <v>0</v>
@@ -9963,12 +9963,12 @@
         <v>1680</v>
       </c>
       <c r="V77" s="44">
-        <f t="shared" si="16"/>
-        <v>118905</v>
+        <f>SUM(N77:U77)</f>
+        <v>121405</v>
       </c>
       <c r="W77" s="44">
-        <f t="shared" si="17"/>
-        <v>59095</v>
+        <f>M77-V77</f>
+        <v>56595</v>
       </c>
       <c r="X77" s="44">
         <f t="shared" si="18"/>
@@ -10032,7 +10032,7 @@
         <v>2400</v>
       </c>
       <c r="O78" s="43">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="P78" s="43">
         <v>0</v>
@@ -10053,12 +10053,12 @@
         <v>0</v>
       </c>
       <c r="V78" s="44">
-        <f t="shared" si="16"/>
-        <v>11850</v>
+        <f>SUM(N78:U78)</f>
+        <v>14350</v>
       </c>
       <c r="W78" s="44">
         <f t="shared" si="17"/>
-        <v>32650</v>
+        <v>30150</v>
       </c>
       <c r="X78" s="44">
         <f t="shared" si="18"/>
@@ -10122,7 +10122,7 @@
         <v>3600</v>
       </c>
       <c r="O79" s="43">
-        <v>15000</v>
+        <v>17500</v>
       </c>
       <c r="P79" s="43">
         <v>0</v>
@@ -10143,12 +10143,12 @@
         <v>0</v>
       </c>
       <c r="V79" s="44">
-        <f t="shared" si="16"/>
-        <v>37964</v>
+        <f>SUM(N79:U79)</f>
+        <v>40464</v>
       </c>
       <c r="W79" s="44">
         <f t="shared" si="17"/>
-        <v>65880</v>
+        <v>63380</v>
       </c>
       <c r="X79" s="44">
         <f t="shared" si="18"/>
@@ -10212,7 +10212,7 @@
         <v>2800</v>
       </c>
       <c r="O80" s="43">
-        <v>5000</v>
+        <v>7500</v>
       </c>
       <c r="P80" s="43">
         <v>0</v>
@@ -10233,12 +10233,12 @@
         <v>0</v>
       </c>
       <c r="V80" s="44">
-        <f t="shared" si="16"/>
-        <v>24060</v>
+        <f>SUM(N80:U80)</f>
+        <v>26560</v>
       </c>
       <c r="W80" s="44">
         <f t="shared" si="17"/>
-        <v>66680</v>
+        <v>64180</v>
       </c>
       <c r="X80" s="44">
         <f t="shared" si="18"/>
@@ -10302,7 +10302,7 @@
         <v>4800</v>
       </c>
       <c r="O81" s="43">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="P81" s="43">
         <v>0</v>
@@ -10323,12 +10323,12 @@
         <v>0</v>
       </c>
       <c r="V81" s="44">
-        <f t="shared" si="16"/>
-        <v>17500</v>
+        <f>SUM(N81:U81)</f>
+        <v>20000</v>
       </c>
       <c r="W81" s="44">
         <f t="shared" si="17"/>
-        <v>84000</v>
+        <v>81500</v>
       </c>
       <c r="X81" s="44">
         <f t="shared" si="18"/>
@@ -10392,7 +10392,7 @@
         <v>3200</v>
       </c>
       <c r="O82" s="43">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="P82" s="43">
         <v>0</v>
@@ -10412,11 +10412,11 @@
       </c>
       <c r="V82" s="44">
         <f t="shared" si="16"/>
-        <v>19783.329900000001</v>
+        <v>22283.329900000001</v>
       </c>
       <c r="W82" s="44">
         <f t="shared" si="17"/>
-        <v>80696.670100000003</v>
+        <v>78196.670100000003</v>
       </c>
       <c r="X82" s="44">
         <f t="shared" si="18"/>
@@ -10480,7 +10480,7 @@
         <v>2400</v>
       </c>
       <c r="O83" s="43">
-        <v>2000</v>
+        <v>4500</v>
       </c>
       <c r="P83" s="43">
         <v>0</v>
@@ -10502,11 +10502,11 @@
       </c>
       <c r="V83" s="44">
         <f t="shared" si="16"/>
-        <v>12900</v>
+        <v>15400</v>
       </c>
       <c r="W83" s="44">
         <f t="shared" si="17"/>
-        <v>24600</v>
+        <v>22100</v>
       </c>
       <c r="X83" s="44">
         <f t="shared" si="18"/>
@@ -10570,7 +10570,7 @@
         <v>2400</v>
       </c>
       <c r="O84" s="43">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="P84" s="43">
         <v>0</v>
@@ -10592,11 +10592,11 @@
       </c>
       <c r="V84" s="44">
         <f t="shared" si="16"/>
-        <v>15890</v>
+        <v>18390</v>
       </c>
       <c r="W84" s="44">
         <f t="shared" si="17"/>
-        <v>66620</v>
+        <v>64120</v>
       </c>
       <c r="X84" s="44">
         <f t="shared" si="18"/>
@@ -10660,7 +10660,7 @@
         <v>2400</v>
       </c>
       <c r="O85" s="43">
-        <v>5000</v>
+        <v>7500</v>
       </c>
       <c r="P85" s="43">
         <v>0</v>
@@ -10682,11 +10682,11 @@
       </c>
       <c r="V85" s="44">
         <f t="shared" si="16"/>
-        <v>11240</v>
+        <v>13740</v>
       </c>
       <c r="W85" s="44">
         <f t="shared" si="17"/>
-        <v>64580</v>
+        <v>62080</v>
       </c>
       <c r="X85" s="44">
         <f t="shared" si="18"/>
@@ -10748,7 +10748,7 @@
         <v>2800</v>
       </c>
       <c r="O86" s="43">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="P86" s="43">
         <v>0</v>
@@ -10770,11 +10770,11 @@
       </c>
       <c r="V86" s="44">
         <f t="shared" si="16"/>
-        <v>9320</v>
+        <v>11820</v>
       </c>
       <c r="W86" s="44">
         <f t="shared" si="17"/>
-        <v>72610</v>
+        <v>70110</v>
       </c>
       <c r="X86" s="44">
         <f t="shared" si="18"/>
@@ -10836,7 +10836,7 @@
         <v>3200</v>
       </c>
       <c r="O87" s="43">
-        <v>15000</v>
+        <v>17500</v>
       </c>
       <c r="P87" s="43">
         <v>0</v>
@@ -10858,11 +10858,11 @@
       </c>
       <c r="V87" s="44">
         <f t="shared" si="16"/>
-        <v>34420</v>
+        <v>36920</v>
       </c>
       <c r="W87" s="44">
         <f t="shared" si="17"/>
-        <v>58780</v>
+        <v>56280</v>
       </c>
       <c r="X87" s="44">
         <f t="shared" si="18"/>
@@ -10926,7 +10926,7 @@
         <v>2400</v>
       </c>
       <c r="O88" s="43">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="P88" s="43">
         <v>0</v>
@@ -10948,11 +10948,11 @@
       </c>
       <c r="V88" s="44">
         <f t="shared" si="16"/>
-        <v>3900</v>
+        <v>6400</v>
       </c>
       <c r="W88" s="44">
         <f t="shared" si="17"/>
-        <v>28600</v>
+        <v>26100</v>
       </c>
       <c r="X88" s="44">
         <f t="shared" si="18"/>
@@ -11014,7 +11014,7 @@
         <v>2400</v>
       </c>
       <c r="O89" s="43">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="P89" s="43">
         <v>0</v>
@@ -11036,11 +11036,11 @@
       </c>
       <c r="V89" s="44">
         <f t="shared" si="16"/>
-        <v>23240</v>
+        <v>25740</v>
       </c>
       <c r="W89" s="44">
         <f t="shared" si="17"/>
-        <v>56040</v>
+        <v>53540</v>
       </c>
       <c r="X89" s="44">
         <f t="shared" si="18"/>
@@ -11104,7 +11104,7 @@
         <v>3200</v>
       </c>
       <c r="O90" s="43">
-        <v>15000</v>
+        <v>17500</v>
       </c>
       <c r="P90" s="43">
         <v>0</v>
@@ -11126,11 +11126,11 @@
       </c>
       <c r="V90" s="44">
         <f t="shared" si="16"/>
-        <v>24920</v>
+        <v>27420</v>
       </c>
       <c r="W90" s="44">
         <f t="shared" si="17"/>
-        <v>74710</v>
+        <v>72210</v>
       </c>
       <c r="X90" s="44">
         <f t="shared" si="18"/>
@@ -11192,7 +11192,7 @@
         <v>2400</v>
       </c>
       <c r="O91" s="43">
-        <v>12000</v>
+        <v>14500</v>
       </c>
       <c r="P91" s="43">
         <v>0</v>
@@ -11214,11 +11214,11 @@
       </c>
       <c r="V91" s="44">
         <f t="shared" si="16"/>
-        <v>15900</v>
+        <v>18400</v>
       </c>
       <c r="W91" s="44">
         <f t="shared" si="17"/>
-        <v>45230</v>
+        <v>42730</v>
       </c>
       <c r="X91" s="44">
         <f t="shared" si="18"/>
@@ -15648,5 +15648,6 @@
   </sheetData>
   <autoFilter ref="A1:Y181" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Salary_Slip 2026-2027.xlsx
+++ b/Salary_Slip 2026-2027.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Hiran\Formats\PayslipApp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Hiran\Formats\PayslipApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F53E9C55-6015-413C-B20A-2E578126F471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6E5DB4A-F4C7-49E0-AD4F-62969DCAB31A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="795" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="795" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Salary Silp" sheetId="1" r:id="rId1"/>
@@ -22,12 +22,25 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Salary Data'!$A$1:$Y$181</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Salary Silp'!$A$1:$E$47</definedName>
   </definedNames>
-  <calcPr calcId="181029" calcMode="autoNoTable"/>
+  <calcPr calcId="191029" calcMode="autoNoTable"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="235">
   <si>
     <t>CAPITAL BRIDGE PRIVATE LIMITED</t>
   </si>
@@ -739,17 +752,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="11">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="#,##0.00;\-#,##0.00;&quot;-&quot;"/>
-    <numFmt numFmtId="165" formatCode="0;\-0;;@"/>
-    <numFmt numFmtId="166" formatCode="&quot;Rs.&quot;#,##0.00"/>
-    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="168" formatCode="&quot;No. &quot;@"/>
-    <numFmt numFmtId="169" formatCode="mmmm\-yyyy"/>
-    <numFmt numFmtId="170" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-    <numFmt numFmtId="171" formatCode="&quot;No. &quot;@\,"/>
-    <numFmt numFmtId="172" formatCode="@\,"/>
-    <numFmt numFmtId="173" formatCode="&quot;Tel: &quot;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00;\-#,##0.00;&quot;-&quot;"/>
+    <numFmt numFmtId="166" formatCode="0;\-0;;@"/>
+    <numFmt numFmtId="167" formatCode="&quot;Rs.&quot;#,##0.00"/>
+    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="169" formatCode="&quot;No. &quot;@"/>
+    <numFmt numFmtId="170" formatCode="mmmm\-yyyy"/>
+    <numFmt numFmtId="171" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="172" formatCode="&quot;No. &quot;@\,"/>
+    <numFmt numFmtId="173" formatCode="@\,"/>
+    <numFmt numFmtId="174" formatCode="&quot;Tel: &quot;@"/>
   </numFmts>
   <fonts count="23" x14ac:knownFonts="1">
     <font>
@@ -1132,8 +1145,8 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1173,28 +1186,28 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1210,16 +1223,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1236,7 +1249,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="169" fontId="14" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="170" fontId="14" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1253,22 +1266,22 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="171" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="171" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="0" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="13" fontId="0" fillId="9" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1320,13 +1333,13 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="173" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1379,9 +1392,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1419,7 +1432,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1525,7 +1538,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1667,7 +1680,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1679,13 +1692,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G47"/>
-  <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="21.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.42578125" style="54" customWidth="1"/>
-    <col min="3" max="16384" width="21.7109375" style="54"/>
+    <col min="2" max="2" width="10.44140625" style="54" customWidth="1"/>
+    <col min="3" max="16384" width="21.6640625" style="54"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1696,7 +1709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -1705,7 +1718,7 @@
       <c r="D2"/>
       <c r="E2"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -1714,13 +1727,13 @@
       <c r="D3"/>
       <c r="E3"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B4"/>
       <c r="C4"/>
       <c r="D4"/>
       <c r="E4"/>
     </row>
-    <row r="5" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
@@ -1735,7 +1748,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>92</v>
       </c>
@@ -1751,7 +1764,7 @@
         <v>46235</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="41" t="str">
         <f>IFERROR(INDEX('Employee Master'!$J:$J,MATCH($A$6,'Employee Master'!$A:$A,0)),"")</f>
         <v>47/7/A</v>
@@ -1765,7 +1778,7 @@
       </c>
       <c r="E7" s="32"/>
     </row>
-    <row r="8" spans="1:7" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="64" t="str">
         <f>IFERROR(INDEX('Employee Master'!$K:$K,MATCH($A$6,'Employee Master'!$A:$A,0)),"")</f>
         <v>Richard Pamunuwa MW</v>
@@ -1780,7 +1793,7 @@
       </c>
       <c r="E8" s="69"/>
     </row>
-    <row r="9" spans="1:7" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="63" t="str">
         <f>IFERROR(INDEX('Employee Master'!$L:$L, MATCH($A$6, 'Employee Master'!$A:$A, 0)) &amp; ".", "")</f>
         <v>Matale.</v>
@@ -1795,7 +1808,7 @@
       </c>
       <c r="E9" s="69"/>
     </row>
-    <row r="10" spans="1:7" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A10" s="65" t="str">
         <f>IFERROR(INDEX('Employee Master'!$N:$N,MATCH($A$6,'Employee Master'!$A:$A,0)),"")</f>
         <v>076-7597550</v>
@@ -1805,7 +1818,7 @@
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
       <c r="B11" s="5"/>
       <c r="C11" s="10" t="s">
@@ -1816,14 +1829,14 @@
       </c>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
     </row>
-    <row r="13" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
         <v>16</v>
       </c>
@@ -1836,7 +1849,7 @@
       <c r="F13" s="55"/>
       <c r="G13" s="56"/>
     </row>
-    <row r="14" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="66" t="s">
         <v>18</v>
       </c>
@@ -1850,7 +1863,7 @@
       <c r="F14" s="55"/>
       <c r="G14" s="58"/>
     </row>
-    <row r="15" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="66" t="s">
         <v>19</v>
       </c>
@@ -1864,7 +1877,7 @@
       <c r="F15" s="55"/>
       <c r="G15" s="56"/>
     </row>
-    <row r="16" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="66" t="s">
         <v>20</v>
       </c>
@@ -1878,7 +1891,7 @@
       <c r="F16" s="55"/>
       <c r="G16" s="56"/>
     </row>
-    <row r="17" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="66" t="s">
         <v>21</v>
       </c>
@@ -1892,7 +1905,7 @@
       <c r="F17" s="55"/>
       <c r="G17" s="56"/>
     </row>
-    <row r="18" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="66" t="s">
         <v>22</v>
       </c>
@@ -1906,7 +1919,7 @@
       <c r="F18" s="55"/>
       <c r="G18" s="59"/>
     </row>
-    <row r="19" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="66" t="s">
         <v>23</v>
       </c>
@@ -1920,7 +1933,7 @@
       <c r="F19" s="55"/>
       <c r="G19" s="59"/>
     </row>
-    <row r="20" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="66" t="s">
         <v>24</v>
       </c>
@@ -1934,7 +1947,7 @@
       <c r="F20" s="55"/>
       <c r="G20" s="58"/>
     </row>
-    <row r="21" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="66" t="s">
         <v>25</v>
       </c>
@@ -1948,7 +1961,7 @@
       <c r="F21" s="55"/>
       <c r="G21" s="56"/>
     </row>
-    <row r="22" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>
       <c r="B22" s="14"/>
       <c r="C22" s="74" t="s">
@@ -1962,14 +1975,14 @@
       <c r="F22" s="55"/>
       <c r="G22" s="59"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
         <v>27</v>
       </c>
@@ -1982,7 +1995,7 @@
       <c r="F24" s="55"/>
       <c r="G24" s="56"/>
     </row>
-    <row r="25" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="66" t="s">
         <v>28</v>
       </c>
@@ -1996,7 +2009,7 @@
       <c r="F25" s="55"/>
       <c r="G25" s="58"/>
     </row>
-    <row r="26" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="66" t="s">
         <v>29</v>
       </c>
@@ -2010,7 +2023,7 @@
       <c r="F26" s="55"/>
       <c r="G26" s="58"/>
     </row>
-    <row r="27" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="66" t="s">
         <v>30</v>
       </c>
@@ -2024,7 +2037,7 @@
       <c r="F27" s="55"/>
       <c r="G27" s="58"/>
     </row>
-    <row r="28" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="66" t="s">
         <v>31</v>
       </c>
@@ -2041,7 +2054,7 @@
       <c r="F28" s="55"/>
       <c r="G28" s="56"/>
     </row>
-    <row r="29" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="66" t="s">
         <v>32</v>
       </c>
@@ -2055,7 +2068,7 @@
       <c r="F29" s="55"/>
       <c r="G29" s="56"/>
     </row>
-    <row r="30" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="66" t="s">
         <v>33</v>
       </c>
@@ -2069,7 +2082,7 @@
       <c r="F30" s="55"/>
       <c r="G30" s="56"/>
     </row>
-    <row r="31" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="66" t="s">
         <v>34</v>
       </c>
@@ -2083,7 +2096,7 @@
       <c r="F31" s="55"/>
       <c r="G31" s="59"/>
     </row>
-    <row r="32" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="66" t="s">
         <v>35</v>
       </c>
@@ -2097,7 +2110,7 @@
       <c r="F32" s="55"/>
       <c r="G32" s="59"/>
     </row>
-    <row r="33" spans="1:7" s="62" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" s="62" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="13"/>
       <c r="B33" s="14"/>
       <c r="C33" s="74" t="s">
@@ -2111,13 +2124,13 @@
       <c r="F33" s="60"/>
       <c r="G33" s="61"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B34"/>
       <c r="C34"/>
       <c r="D34"/>
       <c r="E34"/>
     </row>
-    <row r="35" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="19"/>
       <c r="B35" s="20"/>
       <c r="C35" s="74" t="s">
@@ -2131,13 +2144,13 @@
       <c r="F35" s="55"/>
       <c r="G35" s="59"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B36"/>
       <c r="C36"/>
       <c r="D36"/>
       <c r="E36"/>
     </row>
-    <row r="37" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="17"/>
       <c r="B37" s="18"/>
       <c r="C37" s="72" t="s">
@@ -2153,7 +2166,7 @@
       <c r="F37" s="55"/>
       <c r="G37" s="56"/>
     </row>
-    <row r="38" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" s="57" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="17"/>
       <c r="B38" s="18"/>
       <c r="C38" s="73"/>
@@ -2167,31 +2180,31 @@
       <c r="F38" s="55"/>
       <c r="G38" s="56"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B39"/>
       <c r="C39"/>
       <c r="D39"/>
       <c r="E39"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B40"/>
       <c r="C40"/>
       <c r="D40"/>
       <c r="E40"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B41"/>
       <c r="C41"/>
       <c r="D41"/>
       <c r="E41"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B42"/>
       <c r="C42"/>
       <c r="D42"/>
       <c r="E42"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="70" t="s">
         <v>41</v>
       </c>
@@ -2202,7 +2215,7 @@
       </c>
       <c r="E43" s="71"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="77" t="s">
         <v>42</v>
       </c>
@@ -2213,13 +2226,13 @@
       </c>
       <c r="E44" s="71"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B45"/>
       <c r="C45"/>
       <c r="D45"/>
       <c r="E45"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="78" t="s">
         <v>44</v>
       </c>
@@ -2228,7 +2241,7 @@
       <c r="D46" s="76"/>
       <c r="E46" s="76"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="75" t="s">
         <v>45</v>
       </c>
@@ -2280,7 +2293,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.28999999999999998" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="89" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="90" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -2299,7 +2312,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="12" style="3" customWidth="1"/>
@@ -2308,14 +2321,14 @@
     <col min="5" max="6" width="15" customWidth="1"/>
     <col min="7" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="42" customWidth="1"/>
-    <col min="10" max="10" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.44140625" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="16" customWidth="1"/>
     <col min="15" max="15" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>46</v>
       </c>
@@ -2362,7 +2375,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>60</v>
       </c>
@@ -2409,7 +2422,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>69</v>
       </c>
@@ -2456,7 +2469,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="23" t="s">
         <v>77</v>
       </c>
@@ -2503,7 +2516,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="23" t="s">
         <v>85</v>
       </c>
@@ -2550,7 +2563,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="23" t="s">
         <v>92</v>
       </c>
@@ -2597,7 +2610,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="23" t="s">
         <v>99</v>
       </c>
@@ -2644,7 +2657,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="23" t="s">
         <v>103</v>
       </c>
@@ -2691,7 +2704,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="23" t="s">
         <v>110</v>
       </c>
@@ -2738,7 +2751,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="23" t="s">
         <v>116</v>
       </c>
@@ -2785,7 +2798,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="23" t="s">
         <v>121</v>
       </c>
@@ -2810,7 +2823,7 @@
       </c>
       <c r="H11" s="26">
         <f t="shared" ca="1" si="1"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I11" s="23" t="s">
         <v>123</v>
@@ -2832,7 +2845,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="23" t="s">
         <v>127</v>
       </c>
@@ -2879,7 +2892,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="23" t="s">
         <v>132</v>
       </c>
@@ -2926,7 +2939,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="23" t="s">
         <v>8</v>
       </c>
@@ -2973,7 +2986,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="23" t="s">
         <v>141</v>
       </c>
@@ -3020,7 +3033,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="23" t="s">
         <v>146</v>
       </c>
@@ -3067,19 +3080,19 @@
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D19" s="29"/>
     </row>
-    <row r="21" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D21" s="29"/>
     </row>
-    <row r="23" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D23" s="29"/>
     </row>
-    <row r="25" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D25" s="29"/>
     </row>
-    <row r="27" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D27" s="29"/>
     </row>
   </sheetData>
@@ -3102,7 +3115,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AA182"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -3110,10 +3123,10 @@
     <col min="4" max="4" width="24" customWidth="1"/>
     <col min="5" max="25" width="16" customWidth="1"/>
     <col min="26" max="26" width="12" style="51" customWidth="1"/>
-    <col min="27" max="27" width="32" style="48" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="36.88671875" style="48" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="42" t="s">
         <v>151</v>
       </c>
@@ -3196,7 +3209,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="35">
         <v>46113</v>
       </c>
@@ -3286,7 +3299,7 @@
         <v>46113R A A S Ranasinghe</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="35">
         <v>46113</v>
       </c>
@@ -3376,7 +3389,7 @@
         <v>46113P G U N Wimalasooriya</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="35">
         <v>46113</v>
       </c>
@@ -3466,7 +3479,7 @@
         <v>46113N M A G M Peiris</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="35">
         <v>46113</v>
       </c>
@@ -3556,7 +3569,7 @@
         <v>46113K R T Hemantha</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="35">
         <v>46113</v>
       </c>
@@ -3646,7 +3659,7 @@
         <v>46113W M H M Weerasinghe</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="35">
         <v>46113</v>
       </c>
@@ -3736,7 +3749,7 @@
         <v>46113R W D S Wijerathna</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="35">
         <v>46113</v>
       </c>
@@ -3826,7 +3839,7 @@
         <v>46113S Wathmi Sankalpana</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="35">
         <v>46113</v>
       </c>
@@ -3916,7 +3929,7 @@
         <v>46113E M P P W O R K Jayawardana</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="35">
         <v>46113</v>
       </c>
@@ -4006,7 +4019,7 @@
         <v>46113T M R L B Thennakoon</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="35">
         <v>46113</v>
       </c>
@@ -4094,7 +4107,7 @@
         <v>46113W K Senaverathna</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="35">
         <v>46113</v>
       </c>
@@ -4182,7 +4195,7 @@
         <v>46113D R G S L Ranaweera</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="35">
         <v>46113</v>
       </c>
@@ -4270,7 +4283,7 @@
         <v>46113W A A Heshani Bandara</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="35">
         <v>46113</v>
       </c>
@@ -4360,7 +4373,7 @@
         <v>46113D M T S Disanayake</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="35">
         <v>46113</v>
       </c>
@@ -4448,7 +4461,7 @@
         <v>46113P L D B Wijewardhna</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="35">
         <v>46113</v>
       </c>
@@ -4533,7 +4546,7 @@
         <v>46113N G L D Supunsiri</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="35">
         <v>46143</v>
       </c>
@@ -4623,7 +4636,7 @@
         <v>46143R A A S Ranasinghe</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="35">
         <v>46143</v>
       </c>
@@ -4713,7 +4726,7 @@
         <v>46143P G U N Wimalasooriya</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="35">
         <v>46143</v>
       </c>
@@ -4803,7 +4816,7 @@
         <v>46143N M A G M Peiris</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="35">
         <v>46143</v>
       </c>
@@ -4893,7 +4906,7 @@
         <v>46143K R T Hemantha</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="35">
         <v>46143</v>
       </c>
@@ -4983,7 +4996,7 @@
         <v>46143W M H M Weerasinghe</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="35">
         <v>46143</v>
       </c>
@@ -5073,7 +5086,7 @@
         <v>46143R W D S Wijerathna</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="35">
         <v>46143</v>
       </c>
@@ -5163,7 +5176,7 @@
         <v>46143S Wathmi Sankalpana</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="35">
         <v>46143</v>
       </c>
@@ -5253,7 +5266,7 @@
         <v>46143E M P P W O R K Jayawardana</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="35">
         <v>46143</v>
       </c>
@@ -5343,7 +5356,7 @@
         <v>46143T M R L B Thennakoon</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="35">
         <v>46143</v>
       </c>
@@ -5431,7 +5444,7 @@
         <v>46143W K Senaverathna</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="35">
         <v>46143</v>
       </c>
@@ -5521,7 +5534,7 @@
         <v>46143D R G S L Ranaweera</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="35">
         <v>46143</v>
       </c>
@@ -5609,7 +5622,7 @@
         <v>46143W A A Heshani Bandara</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="35">
         <v>46143</v>
       </c>
@@ -5699,7 +5712,7 @@
         <v>46143D M T S Disanayake</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="35">
         <v>46143</v>
       </c>
@@ -5787,7 +5800,7 @@
         <v>46143P L D B Wijewardhna</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="35">
         <v>46143</v>
       </c>
@@ -5872,7 +5885,7 @@
         <v>46143N G L D Supunsiri</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="35">
         <v>46174</v>
       </c>
@@ -5962,7 +5975,7 @@
         <v>46174R A A S Ranasinghe</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="35">
         <v>46174</v>
       </c>
@@ -6052,7 +6065,7 @@
         <v>46174P G U N Wimalasooriya</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="35">
         <v>46174</v>
       </c>
@@ -6142,7 +6155,7 @@
         <v>46174N M A G M Peiris</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="35">
         <v>46174</v>
       </c>
@@ -6232,7 +6245,7 @@
         <v>46174K R T Hemantha</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="35">
         <v>46174</v>
       </c>
@@ -6322,7 +6335,7 @@
         <v>46174W M H M Weerasinghe</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="35">
         <v>46174</v>
       </c>
@@ -6412,7 +6425,7 @@
         <v>46174R W D S Wijerathna</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="35">
         <v>46174</v>
       </c>
@@ -6502,7 +6515,7 @@
         <v>46174S Wathmi Sankalpana</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="35">
         <v>46174</v>
       </c>
@@ -6592,7 +6605,7 @@
         <v>46174E M P P W O R K Jayawardana</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="35">
         <v>46174</v>
       </c>
@@ -6682,7 +6695,7 @@
         <v>46174T M R L B Thennakoon</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="35">
         <v>46174</v>
       </c>
@@ -6770,7 +6783,7 @@
         <v>46174W K Senaverathna</v>
       </c>
     </row>
-    <row r="42" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="35">
         <v>46174</v>
       </c>
@@ -6860,7 +6873,7 @@
         <v>46174D R G S L Ranaweera</v>
       </c>
     </row>
-    <row r="43" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="35">
         <v>46174</v>
       </c>
@@ -6948,7 +6961,7 @@
         <v>46174W A A Heshani Bandara</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="35">
         <v>46174</v>
       </c>
@@ -7038,7 +7051,7 @@
         <v>46174D M T S Disanayake</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="35">
         <v>46174</v>
       </c>
@@ -7126,7 +7139,7 @@
         <v>46174P L D B Wijewardhna</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="35">
         <v>46174</v>
       </c>
@@ -7214,7 +7227,7 @@
         <v>46174N G L D Supunsiri</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="35">
         <v>46204</v>
       </c>
@@ -7304,7 +7317,7 @@
         <v>46204R A A S Ranasinghe</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="35">
         <v>46204</v>
       </c>
@@ -7394,7 +7407,7 @@
         <v>46204P G U N Wimalasooriya</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="35">
         <v>46204</v>
       </c>
@@ -7484,7 +7497,7 @@
         <v>46204N M A G M Peiris</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="35">
         <v>46204</v>
       </c>
@@ -7574,7 +7587,7 @@
         <v>46204K R T Hemantha</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="35">
         <v>46204</v>
       </c>
@@ -7664,7 +7677,7 @@
         <v>46204W M H M Weerasinghe</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="35">
         <v>46204</v>
       </c>
@@ -7754,7 +7767,7 @@
         <v>46204R W D S Wijerathna</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="35">
         <v>46204</v>
       </c>
@@ -7844,7 +7857,7 @@
         <v>46204S Wathmi Sankalpana</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="35">
         <v>46204</v>
       </c>
@@ -7934,7 +7947,7 @@
         <v>46204E M P P W O R K Jayawardana</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="35">
         <v>46204</v>
       </c>
@@ -8024,7 +8037,7 @@
         <v>46204T M R L B Thennakoon</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="35">
         <v>46204</v>
       </c>
@@ -8112,7 +8125,7 @@
         <v>46204W K Senaverathna</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="35">
         <v>46204</v>
       </c>
@@ -8202,7 +8215,7 @@
         <v>46204D R G S L Ranaweera</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="35">
         <v>46204</v>
       </c>
@@ -8290,7 +8303,7 @@
         <v>46204W A A Heshani Bandara</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="35">
         <v>46204</v>
       </c>
@@ -8380,7 +8393,7 @@
         <v>46204D M T S Disanayake</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="35">
         <v>46204</v>
       </c>
@@ -8468,7 +8481,7 @@
         <v>46204P L D B Wijewardhna</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="35">
         <v>46204</v>
       </c>
@@ -8556,7 +8569,7 @@
         <v>46204N G L D Supunsiri</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="35">
         <v>46235</v>
       </c>
@@ -8646,7 +8659,7 @@
         <v>46235R A A S Ranasinghe</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="35">
         <v>46235</v>
       </c>
@@ -8736,7 +8749,7 @@
         <v>46235P G U N Wimalasooriya</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="35">
         <v>46235</v>
       </c>
@@ -8826,7 +8839,7 @@
         <v>46235N M A G M Peiris</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="35">
         <v>46235</v>
       </c>
@@ -8916,7 +8929,7 @@
         <v>46235K R T Hemantha</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="35">
         <v>46235</v>
       </c>
@@ -9006,7 +9019,7 @@
         <v>46235W M H M Weerasinghe</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="35">
         <v>46235</v>
       </c>
@@ -9096,7 +9109,7 @@
         <v>46235R W D S Wijerathna</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="35">
         <v>46235</v>
       </c>
@@ -9186,7 +9199,7 @@
         <v>46235S Wathmi Sankalpana</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="35">
         <v>46235</v>
       </c>
@@ -9276,7 +9289,7 @@
         <v>46235E M P P W O R K Jayawardana</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="35">
         <v>46235</v>
       </c>
@@ -9364,7 +9377,7 @@
         <v>46235T M R L B Thennakoon</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="35">
         <v>46235</v>
       </c>
@@ -9452,7 +9465,7 @@
         <v>46235W K Senaverathna</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="35">
         <v>46235</v>
       </c>
@@ -9542,7 +9555,7 @@
         <v>46235D R G S L Ranaweera</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="35">
         <v>46235</v>
       </c>
@@ -9630,7 +9643,7 @@
         <v>46235W A A Heshani Bandara</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="35">
         <v>46235</v>
       </c>
@@ -9720,7 +9733,7 @@
         <v>46235D M T S Disanayake</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="35">
         <v>46235</v>
       </c>
@@ -9808,7 +9821,7 @@
         <v>46235P L D B Wijewardhna</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="35">
         <v>46235</v>
       </c>
@@ -9896,7 +9909,7 @@
         <v>46235N G L D Supunsiri</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="35">
         <v>46266</v>
       </c>
@@ -9986,7 +9999,7 @@
         <v>46266R A A S Ranasinghe</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="35">
         <v>46266</v>
       </c>
@@ -10076,7 +10089,7 @@
         <v>46266P G U N Wimalasooriya</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="35">
         <v>46266</v>
       </c>
@@ -10166,7 +10179,7 @@
         <v>46266N M A G M Peiris</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="35">
         <v>46266</v>
       </c>
@@ -10256,7 +10269,7 @@
         <v>46266K R T Hemantha</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="35">
         <v>46266</v>
       </c>
@@ -10346,7 +10359,7 @@
         <v>46266W M H M Weerasinghe</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="35">
         <v>46266</v>
       </c>
@@ -10434,7 +10447,7 @@
         <v>46266R W D S Wijerathna</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="35">
         <v>46266</v>
       </c>
@@ -10524,7 +10537,7 @@
         <v>46266S Wathmi Sankalpana</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="35">
         <v>46266</v>
       </c>
@@ -10614,7 +10627,7 @@
         <v>46266E M P P W O R K Jayawardana</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="35">
         <v>46266</v>
       </c>
@@ -10702,7 +10715,7 @@
         <v>46266T M R L B Thennakoon</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="35">
         <v>46266</v>
       </c>
@@ -10790,7 +10803,7 @@
         <v>46266W K Senaverathna</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="35">
         <v>46266</v>
       </c>
@@ -10880,7 +10893,7 @@
         <v>46266D R G S L Ranaweera</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="35">
         <v>46266</v>
       </c>
@@ -10968,7 +10981,7 @@
         <v>46266W A A Heshani Bandara</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="35">
         <v>46266</v>
       </c>
@@ -11058,7 +11071,7 @@
         <v>46266D M T S Disanayake</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="35">
         <v>46266</v>
       </c>
@@ -11146,7 +11159,7 @@
         <v>46266P L D B Wijewardhna</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="35">
         <v>46266</v>
       </c>
@@ -11234,742 +11247,1327 @@
         <v>46266N G L D Supunsiri</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="35" t="s">
         <v>207</v>
       </c>
-      <c r="E92" s="43"/>
-      <c r="F92" s="43"/>
-      <c r="G92" s="43"/>
-      <c r="H92" s="43"/>
-      <c r="I92" s="43"/>
-      <c r="J92" s="43"/>
-      <c r="K92" s="43"/>
-      <c r="L92" s="43"/>
+      <c r="B92" t="s">
+        <v>60</v>
+      </c>
+      <c r="C92">
+        <v>5</v>
+      </c>
+      <c r="D92" t="s">
+        <v>61</v>
+      </c>
+      <c r="E92" s="43">
+        <v>61500</v>
+      </c>
+      <c r="F92" s="43">
+        <v>3500</v>
+      </c>
+      <c r="G92" s="43">
+        <v>53000</v>
+      </c>
+      <c r="H92" s="43">
+        <v>0</v>
+      </c>
+      <c r="I92" s="43">
+        <v>29000</v>
+      </c>
+      <c r="J92" s="43">
+        <v>30000</v>
+      </c>
+      <c r="K92" s="43">
+        <v>1000</v>
+      </c>
+      <c r="L92" s="43">
+        <v>0</v>
+      </c>
       <c r="M92" s="44">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>178000</v>
       </c>
       <c r="N92" s="44">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="O92" s="43"/>
-      <c r="P92" s="43"/>
-      <c r="Q92" s="43"/>
-      <c r="R92" s="43"/>
-      <c r="S92" s="43"/>
-      <c r="T92" s="43"/>
-      <c r="U92" s="43"/>
+        <v>5200</v>
+      </c>
+      <c r="O92" s="43">
+        <v>101850</v>
+      </c>
+      <c r="P92" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="43">
+        <v>9250</v>
+      </c>
+      <c r="R92" s="43">
+        <v>2590</v>
+      </c>
+      <c r="S92" s="43">
+        <v>0</v>
+      </c>
+      <c r="T92" s="43">
+        <v>0</v>
+      </c>
+      <c r="U92" s="43">
+        <v>1680</v>
+      </c>
       <c r="V92" s="44">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>120570</v>
       </c>
       <c r="W92" s="44">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>57430</v>
       </c>
       <c r="X92" s="44">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>7800</v>
       </c>
       <c r="Y92" s="44">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>1950</v>
       </c>
       <c r="Z92" s="50"/>
       <c r="AA92" s="47" t="str">
         <f t="shared" si="20"/>
-        <v>October 2026</v>
-      </c>
-    </row>
-    <row r="93" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>October 2026R A A S Ranasinghe</v>
+      </c>
+    </row>
+    <row r="93" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="35" t="s">
         <v>207</v>
       </c>
-      <c r="E93" s="43"/>
-      <c r="F93" s="43"/>
-      <c r="G93" s="43"/>
-      <c r="H93" s="43"/>
-      <c r="I93" s="43"/>
-      <c r="J93" s="43"/>
-      <c r="K93" s="43"/>
-      <c r="L93" s="43"/>
+      <c r="B93" t="s">
+        <v>69</v>
+      </c>
+      <c r="C93">
+        <v>10</v>
+      </c>
+      <c r="D93" t="s">
+        <v>70</v>
+      </c>
+      <c r="E93" s="43">
+        <v>26500</v>
+      </c>
+      <c r="F93" s="43">
+        <v>3500</v>
+      </c>
+      <c r="G93" s="43">
+        <v>5000</v>
+      </c>
+      <c r="H93" s="43">
+        <v>0</v>
+      </c>
+      <c r="I93" s="43">
+        <v>7000</v>
+      </c>
+      <c r="J93" s="43">
+        <v>0</v>
+      </c>
+      <c r="K93" s="43">
+        <v>1000</v>
+      </c>
+      <c r="L93" s="43">
+        <v>4382.5292845833337</v>
+      </c>
       <c r="M93" s="44">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>47382.529284583332</v>
       </c>
       <c r="N93" s="44">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="O93" s="43"/>
-      <c r="P93" s="43"/>
-      <c r="Q93" s="43"/>
-      <c r="R93" s="43"/>
-      <c r="S93" s="43"/>
-      <c r="T93" s="43"/>
-      <c r="U93" s="43"/>
+        <v>2400</v>
+      </c>
+      <c r="O93" s="43">
+        <v>5350</v>
+      </c>
+      <c r="P93" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="43">
+        <v>7500</v>
+      </c>
+      <c r="R93" s="43">
+        <v>225</v>
+      </c>
+      <c r="S93" s="43">
+        <v>0</v>
+      </c>
+      <c r="T93" s="43">
+        <v>4382.5292845833337</v>
+      </c>
+      <c r="U93" s="43">
+        <v>0</v>
+      </c>
       <c r="V93" s="44">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>19857.529284583332</v>
       </c>
       <c r="W93" s="44">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>27525</v>
       </c>
       <c r="X93" s="44">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="Y93" s="44">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="Z93" s="50"/>
       <c r="AA93" s="47" t="str">
         <f t="shared" si="20"/>
-        <v>October 2026</v>
-      </c>
-    </row>
-    <row r="94" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>October 2026P G U N Wimalasooriya</v>
+      </c>
+    </row>
+    <row r="94" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="35" t="s">
         <v>207</v>
       </c>
-      <c r="E94" s="43"/>
-      <c r="F94" s="43"/>
-      <c r="G94" s="43"/>
-      <c r="H94" s="43"/>
-      <c r="I94" s="43"/>
-      <c r="J94" s="43"/>
-      <c r="K94" s="43"/>
-      <c r="L94" s="43"/>
+      <c r="B94" t="s">
+        <v>77</v>
+      </c>
+      <c r="C94">
+        <v>16</v>
+      </c>
+      <c r="D94" t="s">
+        <v>78</v>
+      </c>
+      <c r="E94" s="43">
+        <v>41500</v>
+      </c>
+      <c r="F94" s="43">
+        <v>3500</v>
+      </c>
+      <c r="G94" s="43">
+        <v>17000</v>
+      </c>
+      <c r="H94" s="43">
+        <v>8000</v>
+      </c>
+      <c r="I94" s="43">
+        <v>28980</v>
+      </c>
+      <c r="J94" s="43">
+        <v>0</v>
+      </c>
+      <c r="K94" s="43">
+        <v>1000</v>
+      </c>
+      <c r="L94" s="43">
+        <v>19899.09</v>
+      </c>
       <c r="M94" s="44">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>119879.09</v>
       </c>
       <c r="N94" s="44">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="O94" s="43"/>
-      <c r="P94" s="43"/>
-      <c r="Q94" s="43"/>
-      <c r="R94" s="43"/>
-      <c r="S94" s="43"/>
-      <c r="T94" s="43"/>
-      <c r="U94" s="43"/>
+        <v>3600</v>
+      </c>
+      <c r="O94" s="43">
+        <v>37850</v>
+      </c>
+      <c r="P94" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="43">
+        <v>12500</v>
+      </c>
+      <c r="R94" s="43">
+        <v>2625</v>
+      </c>
+      <c r="S94" s="43">
+        <v>0</v>
+      </c>
+      <c r="T94" s="43">
+        <v>19899.09</v>
+      </c>
+      <c r="U94" s="43">
+        <v>0</v>
+      </c>
       <c r="V94" s="44">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>76474.09</v>
       </c>
       <c r="W94" s="44">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>43405</v>
       </c>
       <c r="X94" s="44">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="Y94" s="44">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>1350</v>
       </c>
       <c r="Z94" s="50"/>
       <c r="AA94" s="47" t="str">
         <f t="shared" si="20"/>
-        <v>October 2026</v>
-      </c>
-    </row>
-    <row r="95" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>October 2026N M A G M Peiris</v>
+      </c>
+    </row>
+    <row r="95" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="35" t="s">
         <v>207</v>
       </c>
-      <c r="E95" s="43"/>
-      <c r="F95" s="43"/>
-      <c r="G95" s="43"/>
-      <c r="H95" s="43"/>
-      <c r="I95" s="43"/>
-      <c r="J95" s="43"/>
-      <c r="K95" s="43"/>
-      <c r="L95" s="43"/>
+      <c r="B95" t="s">
+        <v>85</v>
+      </c>
+      <c r="C95">
+        <v>17</v>
+      </c>
+      <c r="D95" t="s">
+        <v>86</v>
+      </c>
+      <c r="E95" s="43">
+        <v>31500</v>
+      </c>
+      <c r="F95" s="43">
+        <v>3500</v>
+      </c>
+      <c r="G95" s="43">
+        <v>7500</v>
+      </c>
+      <c r="H95" s="43">
+        <v>5000</v>
+      </c>
+      <c r="I95" s="43">
+        <v>28980</v>
+      </c>
+      <c r="J95" s="43">
+        <v>10000</v>
+      </c>
+      <c r="K95" s="43">
+        <v>1000</v>
+      </c>
+      <c r="L95" s="43">
+        <v>15167.33</v>
+      </c>
       <c r="M95" s="44">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>102647.33</v>
       </c>
       <c r="N95" s="44">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="O95" s="43"/>
-      <c r="P95" s="43"/>
-      <c r="Q95" s="43"/>
-      <c r="R95" s="43"/>
-      <c r="S95" s="43"/>
-      <c r="T95" s="43"/>
-      <c r="U95" s="43"/>
+        <v>2800</v>
+      </c>
+      <c r="O95" s="43">
+        <v>12850</v>
+      </c>
+      <c r="P95" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q95" s="43">
+        <v>10000</v>
+      </c>
+      <c r="R95" s="43">
+        <v>2700</v>
+      </c>
+      <c r="S95" s="43">
+        <v>0</v>
+      </c>
+      <c r="T95" s="43">
+        <v>15167.33</v>
+      </c>
+      <c r="U95" s="43">
+        <v>0</v>
+      </c>
       <c r="V95" s="44">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>43517.33</v>
       </c>
       <c r="W95" s="44">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>59130</v>
       </c>
       <c r="X95" s="44">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="Y95" s="44">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>1050</v>
       </c>
       <c r="Z95" s="50"/>
       <c r="AA95" s="47" t="str">
         <f t="shared" si="20"/>
-        <v>October 2026</v>
-      </c>
-    </row>
-    <row r="96" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>October 2026K R T Hemantha</v>
+      </c>
+    </row>
+    <row r="96" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="35" t="s">
         <v>207</v>
       </c>
-      <c r="E96" s="43"/>
-      <c r="F96" s="43"/>
-      <c r="G96" s="43"/>
-      <c r="H96" s="43"/>
-      <c r="I96" s="43"/>
-      <c r="J96" s="43"/>
-      <c r="K96" s="43"/>
-      <c r="L96" s="43"/>
+      <c r="B96" t="s">
+        <v>92</v>
+      </c>
+      <c r="C96">
+        <v>18</v>
+      </c>
+      <c r="D96" t="s">
+        <v>93</v>
+      </c>
+      <c r="E96" s="43">
+        <v>56500</v>
+      </c>
+      <c r="F96" s="43">
+        <v>3500</v>
+      </c>
+      <c r="G96" s="43">
+        <v>26000</v>
+      </c>
+      <c r="H96" s="43">
+        <v>0</v>
+      </c>
+      <c r="I96" s="43">
+        <v>13000</v>
+      </c>
+      <c r="J96" s="43">
+        <v>0</v>
+      </c>
+      <c r="K96" s="43">
+        <v>1000</v>
+      </c>
+      <c r="L96" s="43">
+        <v>4382.5292845833337</v>
+      </c>
       <c r="M96" s="44">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>104382.52928458333</v>
       </c>
       <c r="N96" s="44">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="O96" s="43"/>
-      <c r="P96" s="43"/>
-      <c r="Q96" s="43"/>
-      <c r="R96" s="43"/>
-      <c r="S96" s="43"/>
-      <c r="T96" s="43"/>
-      <c r="U96" s="43"/>
+        <v>4800</v>
+      </c>
+      <c r="O96" s="43">
+        <v>51850</v>
+      </c>
+      <c r="P96" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="43">
+        <v>10000</v>
+      </c>
+      <c r="R96" s="43">
+        <v>900</v>
+      </c>
+      <c r="S96" s="43">
+        <v>0</v>
+      </c>
+      <c r="T96" s="43">
+        <v>4382.5292845833337</v>
+      </c>
+      <c r="U96" s="43">
+        <v>0</v>
+      </c>
       <c r="V96" s="44">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>71932.529284583332</v>
       </c>
       <c r="W96" s="44">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>32450</v>
       </c>
       <c r="X96" s="44">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>7200</v>
       </c>
       <c r="Y96" s="44">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="Z96" s="50"/>
       <c r="AA96" s="47" t="str">
         <f t="shared" si="20"/>
-        <v>October 2026</v>
-      </c>
-    </row>
-    <row r="97" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>October 2026W M H M Weerasinghe</v>
+      </c>
+    </row>
+    <row r="97" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="35" t="s">
         <v>207</v>
       </c>
-      <c r="E97" s="43"/>
-      <c r="F97" s="43"/>
-      <c r="G97" s="43"/>
-      <c r="H97" s="43"/>
-      <c r="I97" s="43"/>
-      <c r="J97" s="43"/>
-      <c r="K97" s="43"/>
-      <c r="L97" s="43"/>
+      <c r="B97" t="s">
+        <v>99</v>
+      </c>
+      <c r="C97">
+        <v>19</v>
+      </c>
+      <c r="D97" t="s">
+        <v>86</v>
+      </c>
+      <c r="E97" s="43">
+        <v>36500</v>
+      </c>
+      <c r="F97" s="43">
+        <v>3500</v>
+      </c>
+      <c r="G97" s="43">
+        <v>7500</v>
+      </c>
+      <c r="H97" s="43">
+        <v>5000</v>
+      </c>
+      <c r="I97" s="43">
+        <v>28980</v>
+      </c>
+      <c r="J97" s="43">
+        <v>10000</v>
+      </c>
+      <c r="K97" s="43">
+        <v>1000</v>
+      </c>
+      <c r="L97" s="43">
+        <v>11195.698333333334</v>
+      </c>
       <c r="M97" s="44">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>103675.69833333333</v>
       </c>
       <c r="N97" s="44">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="O97" s="43"/>
-      <c r="P97" s="43"/>
-      <c r="Q97" s="43"/>
-      <c r="R97" s="43"/>
-      <c r="S97" s="43"/>
-      <c r="T97" s="43"/>
-      <c r="U97" s="43"/>
+        <v>3200</v>
+      </c>
+      <c r="O97" s="43">
+        <v>1850</v>
+      </c>
+      <c r="P97" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="43">
+        <v>0</v>
+      </c>
+      <c r="R97" s="43">
+        <v>0</v>
+      </c>
+      <c r="S97" s="43">
+        <v>0</v>
+      </c>
+      <c r="T97" s="43">
+        <v>11195.698333333334</v>
+      </c>
+      <c r="U97" s="43">
+        <v>0</v>
+      </c>
       <c r="V97" s="44">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>16245.698333333334</v>
       </c>
       <c r="W97" s="44">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>87430</v>
       </c>
       <c r="X97" s="44">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="Y97" s="44">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="Z97" s="50"/>
       <c r="AA97" s="47" t="str">
         <f t="shared" si="20"/>
-        <v>October 2026</v>
-      </c>
-    </row>
-    <row r="98" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>October 2026R W D S Wijerathna</v>
+      </c>
+    </row>
+    <row r="98" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="35" t="s">
         <v>207</v>
       </c>
-      <c r="E98" s="43"/>
-      <c r="F98" s="43"/>
-      <c r="G98" s="43"/>
-      <c r="H98" s="43"/>
-      <c r="I98" s="43"/>
-      <c r="J98" s="43"/>
-      <c r="K98" s="43"/>
-      <c r="L98" s="43"/>
+      <c r="B98" t="s">
+        <v>103</v>
+      </c>
+      <c r="C98">
+        <v>21</v>
+      </c>
+      <c r="D98" t="s">
+        <v>104</v>
+      </c>
+      <c r="E98" s="43">
+        <v>26500</v>
+      </c>
+      <c r="F98" s="43">
+        <v>3500</v>
+      </c>
+      <c r="G98" s="43">
+        <v>0</v>
+      </c>
+      <c r="H98" s="43">
+        <v>0</v>
+      </c>
+      <c r="I98" s="43">
+        <v>5000</v>
+      </c>
+      <c r="J98" s="43">
+        <v>0</v>
+      </c>
+      <c r="K98" s="43">
+        <v>1000</v>
+      </c>
+      <c r="L98" s="43">
+        <v>4382.5292845833337</v>
+      </c>
       <c r="M98" s="44">
         <f t="shared" ref="M98:M129" si="21">SUM(E98:L98)</f>
-        <v>0</v>
+        <v>40382.529284583332</v>
       </c>
       <c r="N98" s="44">
         <f t="shared" ref="N98:N129" si="22">(E98+F98)*8%</f>
-        <v>0</v>
-      </c>
-      <c r="O98" s="43"/>
-      <c r="P98" s="43"/>
-      <c r="Q98" s="43"/>
-      <c r="R98" s="43"/>
-      <c r="S98" s="43"/>
-      <c r="T98" s="43"/>
-      <c r="U98" s="43"/>
+        <v>2400</v>
+      </c>
+      <c r="O98" s="43">
+        <v>3850</v>
+      </c>
+      <c r="P98" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="43">
+        <v>6250</v>
+      </c>
+      <c r="R98" s="43">
+        <v>562.5</v>
+      </c>
+      <c r="S98" s="43">
+        <v>0</v>
+      </c>
+      <c r="T98" s="43">
+        <v>4382.5292845833337</v>
+      </c>
+      <c r="U98" s="43">
+        <v>0</v>
+      </c>
       <c r="V98" s="44">
         <f t="shared" ref="V98:V129" si="23">SUM(N98:U98)</f>
-        <v>0</v>
+        <v>17445.029284583332</v>
       </c>
       <c r="W98" s="44">
         <f t="shared" ref="W98:W129" si="24">M98-V98</f>
-        <v>0</v>
+        <v>22937.5</v>
       </c>
       <c r="X98" s="44">
         <f t="shared" ref="X98:X129" si="25">(E98+F98)*12%</f>
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="Y98" s="44">
         <f t="shared" ref="Y98:Y129" si="26">(E98+F98)*3%</f>
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="Z98" s="50"/>
       <c r="AA98" s="47" t="str">
         <f t="shared" ref="AA98:AA129" si="27">A98&amp;B98</f>
-        <v>October 2026</v>
-      </c>
-    </row>
-    <row r="99" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>October 2026S Wathmi Sankalpana</v>
+      </c>
+    </row>
+    <row r="99" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" s="35" t="s">
         <v>207</v>
       </c>
-      <c r="E99" s="43"/>
-      <c r="F99" s="43"/>
-      <c r="G99" s="43"/>
-      <c r="H99" s="43"/>
-      <c r="I99" s="43"/>
-      <c r="J99" s="43"/>
-      <c r="K99" s="43"/>
-      <c r="L99" s="43"/>
+      <c r="B99" t="s">
+        <v>110</v>
+      </c>
+      <c r="C99">
+        <v>22</v>
+      </c>
+      <c r="D99" t="s">
+        <v>111</v>
+      </c>
+      <c r="E99" s="43">
+        <v>26500</v>
+      </c>
+      <c r="F99" s="43">
+        <v>3500</v>
+      </c>
+      <c r="G99" s="43">
+        <v>5000</v>
+      </c>
+      <c r="H99" s="43">
+        <v>2760</v>
+      </c>
+      <c r="I99" s="43">
+        <v>26910</v>
+      </c>
+      <c r="J99" s="43">
+        <v>10000</v>
+      </c>
+      <c r="K99" s="43">
+        <v>1000</v>
+      </c>
+      <c r="L99" s="43">
+        <v>15081.56</v>
+      </c>
       <c r="M99" s="44">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>90751.56</v>
       </c>
       <c r="N99" s="44">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="O99" s="43"/>
-      <c r="P99" s="43"/>
-      <c r="Q99" s="43"/>
-      <c r="R99" s="43"/>
-      <c r="S99" s="43"/>
-      <c r="T99" s="43"/>
-      <c r="U99" s="43"/>
+        <v>2400</v>
+      </c>
+      <c r="O99" s="43">
+        <v>11850</v>
+      </c>
+      <c r="P99" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="43">
+        <v>5000</v>
+      </c>
+      <c r="R99" s="43">
+        <v>1500</v>
+      </c>
+      <c r="S99" s="43">
+        <v>0</v>
+      </c>
+      <c r="T99" s="43">
+        <v>15081.56</v>
+      </c>
+      <c r="U99" s="43">
+        <v>0</v>
+      </c>
       <c r="V99" s="44">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>35831.56</v>
       </c>
       <c r="W99" s="44">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>54920</v>
       </c>
       <c r="X99" s="44">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="Y99" s="44">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="Z99" s="50"/>
       <c r="AA99" s="47" t="str">
         <f t="shared" si="27"/>
-        <v>October 2026</v>
-      </c>
-    </row>
-    <row r="100" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>October 2026E M P P W O R K Jayawardana</v>
+      </c>
+    </row>
+    <row r="100" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="35" t="s">
         <v>207</v>
       </c>
-      <c r="E100" s="43"/>
-      <c r="F100" s="43"/>
-      <c r="G100" s="43"/>
-      <c r="H100" s="43"/>
-      <c r="I100" s="43"/>
-      <c r="J100" s="43"/>
-      <c r="K100" s="43"/>
-      <c r="L100" s="43"/>
+      <c r="B100" t="s">
+        <v>116</v>
+      </c>
+      <c r="C100">
+        <v>23</v>
+      </c>
+      <c r="D100" t="s">
+        <v>111</v>
+      </c>
+      <c r="E100" s="43">
+        <v>26500</v>
+      </c>
+      <c r="F100" s="43">
+        <v>3500</v>
+      </c>
+      <c r="G100" s="43">
+        <v>7000</v>
+      </c>
+      <c r="H100" s="43">
+        <v>5000</v>
+      </c>
+      <c r="I100" s="43">
+        <v>28980</v>
+      </c>
+      <c r="J100" s="43">
+        <v>0</v>
+      </c>
+      <c r="K100" s="43">
+        <v>1000</v>
+      </c>
+      <c r="L100" s="43">
+        <v>17222.8</v>
+      </c>
       <c r="M100" s="44">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>89202.8</v>
       </c>
       <c r="N100" s="44">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="O100" s="43"/>
-      <c r="P100" s="43"/>
-      <c r="Q100" s="43"/>
-      <c r="R100" s="43"/>
-      <c r="S100" s="43"/>
-      <c r="T100" s="43"/>
-      <c r="U100" s="43"/>
+        <v>2400</v>
+      </c>
+      <c r="O100" s="43">
+        <v>7850</v>
+      </c>
+      <c r="P100" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="43">
+        <v>0</v>
+      </c>
+      <c r="R100" s="43">
+        <v>0</v>
+      </c>
+      <c r="S100" s="43">
+        <v>0</v>
+      </c>
+      <c r="T100" s="43">
+        <v>17222.8</v>
+      </c>
+      <c r="U100" s="43">
+        <v>0</v>
+      </c>
       <c r="V100" s="44">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>27472.799999999999</v>
       </c>
       <c r="W100" s="44">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>61730</v>
       </c>
       <c r="X100" s="44">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="Y100" s="44">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="Z100" s="50"/>
       <c r="AA100" s="47" t="str">
         <f t="shared" si="27"/>
-        <v>October 2026</v>
-      </c>
-    </row>
-    <row r="101" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>October 2026T M R L B Thennakoon</v>
+      </c>
+    </row>
+    <row r="101" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="35" t="s">
         <v>207</v>
       </c>
-      <c r="E101" s="43"/>
-      <c r="F101" s="43"/>
-      <c r="G101" s="43"/>
-      <c r="H101" s="43"/>
-      <c r="I101" s="43"/>
-      <c r="J101" s="43"/>
-      <c r="K101" s="43"/>
-      <c r="L101" s="43"/>
+      <c r="B101" t="s">
+        <v>121</v>
+      </c>
+      <c r="C101">
+        <v>24</v>
+      </c>
+      <c r="D101" t="s">
+        <v>86</v>
+      </c>
+      <c r="E101" s="43">
+        <v>31500</v>
+      </c>
+      <c r="F101" s="43">
+        <v>3500</v>
+      </c>
+      <c r="G101" s="43">
+        <v>7500</v>
+      </c>
+      <c r="H101" s="43">
+        <v>5000</v>
+      </c>
+      <c r="I101" s="43">
+        <v>26910</v>
+      </c>
+      <c r="J101" s="43">
+        <v>0</v>
+      </c>
+      <c r="K101" s="43">
+        <v>1000</v>
+      </c>
+      <c r="L101" s="43">
+        <v>10292.66</v>
+      </c>
       <c r="M101" s="44">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>85702.66</v>
       </c>
       <c r="N101" s="44">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="O101" s="43"/>
-      <c r="P101" s="43"/>
-      <c r="Q101" s="43"/>
-      <c r="R101" s="43"/>
-      <c r="S101" s="43"/>
-      <c r="T101" s="43"/>
-      <c r="U101" s="43"/>
+        <v>2800</v>
+      </c>
+      <c r="O101" s="43">
+        <v>6850</v>
+      </c>
+      <c r="P101" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="43">
+        <v>0</v>
+      </c>
+      <c r="R101" s="43">
+        <v>0</v>
+      </c>
+      <c r="S101" s="43">
+        <v>0</v>
+      </c>
+      <c r="T101" s="43">
+        <v>10292.66</v>
+      </c>
+      <c r="U101" s="43">
+        <v>0</v>
+      </c>
       <c r="V101" s="44">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>19942.66</v>
       </c>
       <c r="W101" s="44">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>65760</v>
       </c>
       <c r="X101" s="44">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="Y101" s="44">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>1050</v>
       </c>
       <c r="Z101" s="50"/>
       <c r="AA101" s="47" t="str">
         <f t="shared" si="27"/>
-        <v>October 2026</v>
-      </c>
-    </row>
-    <row r="102" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>October 2026W K Senaverathna</v>
+      </c>
+    </row>
+    <row r="102" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="35" t="s">
         <v>207</v>
       </c>
-      <c r="E102" s="43"/>
-      <c r="F102" s="43"/>
-      <c r="G102" s="43"/>
-      <c r="H102" s="43"/>
-      <c r="I102" s="43"/>
-      <c r="J102" s="43"/>
-      <c r="K102" s="43"/>
-      <c r="L102" s="43"/>
+      <c r="B102" t="s">
+        <v>127</v>
+      </c>
+      <c r="C102">
+        <v>25</v>
+      </c>
+      <c r="D102" t="s">
+        <v>86</v>
+      </c>
+      <c r="E102" s="43">
+        <v>36500</v>
+      </c>
+      <c r="F102" s="43">
+        <v>3500</v>
+      </c>
+      <c r="G102" s="43">
+        <v>5000</v>
+      </c>
+      <c r="H102" s="43">
+        <v>5000</v>
+      </c>
+      <c r="I102" s="43">
+        <v>28980</v>
+      </c>
+      <c r="J102" s="43">
+        <v>10000</v>
+      </c>
+      <c r="K102" s="43">
+        <v>1000</v>
+      </c>
+      <c r="L102" s="43">
+        <v>7511.88</v>
+      </c>
       <c r="M102" s="44">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>97491.88</v>
       </c>
       <c r="N102" s="44">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="O102" s="43"/>
-      <c r="P102" s="43"/>
-      <c r="Q102" s="43"/>
-      <c r="R102" s="43"/>
-      <c r="S102" s="43"/>
-      <c r="T102" s="43"/>
-      <c r="U102" s="43"/>
+        <v>3200</v>
+      </c>
+      <c r="O102" s="43">
+        <v>21850</v>
+      </c>
+      <c r="P102" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="43">
+        <v>10000</v>
+      </c>
+      <c r="R102" s="43">
+        <v>2700</v>
+      </c>
+      <c r="S102" s="43">
+        <v>0</v>
+      </c>
+      <c r="T102" s="43">
+        <v>7511.88</v>
+      </c>
+      <c r="U102" s="43">
+        <v>0</v>
+      </c>
       <c r="V102" s="44">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>45261.88</v>
       </c>
       <c r="W102" s="44">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>52230.000000000007</v>
       </c>
       <c r="X102" s="44">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="Y102" s="44">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="Z102" s="50"/>
       <c r="AA102" s="47" t="str">
         <f t="shared" si="27"/>
-        <v>October 2026</v>
-      </c>
-    </row>
-    <row r="103" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>October 2026D R G S L Ranaweera</v>
+      </c>
+    </row>
+    <row r="103" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="35" t="s">
         <v>207</v>
       </c>
-      <c r="E103" s="43"/>
-      <c r="F103" s="43"/>
-      <c r="G103" s="43"/>
-      <c r="H103" s="43"/>
-      <c r="I103" s="43"/>
-      <c r="J103" s="43"/>
-      <c r="K103" s="43"/>
-      <c r="L103" s="43"/>
+      <c r="B103" t="s">
+        <v>132</v>
+      </c>
+      <c r="C103">
+        <v>26</v>
+      </c>
+      <c r="D103" t="s">
+        <v>104</v>
+      </c>
+      <c r="E103" s="43">
+        <v>26500</v>
+      </c>
+      <c r="F103" s="43">
+        <v>3500</v>
+      </c>
+      <c r="G103" s="43">
+        <v>0</v>
+      </c>
+      <c r="H103" s="43">
+        <v>0</v>
+      </c>
+      <c r="I103" s="43">
+        <v>0</v>
+      </c>
+      <c r="J103" s="43">
+        <v>0</v>
+      </c>
+      <c r="K103" s="43">
+        <v>1000</v>
+      </c>
+      <c r="L103" s="43">
+        <v>4382.5292845833337</v>
+      </c>
       <c r="M103" s="44">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>35382.529284583332</v>
       </c>
       <c r="N103" s="44">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="O103" s="43"/>
-      <c r="P103" s="43"/>
-      <c r="Q103" s="43"/>
-      <c r="R103" s="43"/>
-      <c r="S103" s="43"/>
-      <c r="T103" s="43"/>
-      <c r="U103" s="43"/>
+        <v>2400</v>
+      </c>
+      <c r="O103" s="43">
+        <v>1850</v>
+      </c>
+      <c r="P103" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q103" s="43">
+        <v>0</v>
+      </c>
+      <c r="R103" s="43">
+        <v>0</v>
+      </c>
+      <c r="S103" s="43">
+        <v>0</v>
+      </c>
+      <c r="T103" s="43">
+        <v>4382.5292845833337</v>
+      </c>
+      <c r="U103" s="43">
+        <v>0</v>
+      </c>
       <c r="V103" s="44">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>8632.5292845833337</v>
       </c>
       <c r="W103" s="44">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>26750</v>
       </c>
       <c r="X103" s="44">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="Y103" s="44">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="Z103" s="50"/>
       <c r="AA103" s="47" t="str">
         <f t="shared" si="27"/>
-        <v>October 2026</v>
-      </c>
-    </row>
-    <row r="104" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>October 2026W A A Heshani Bandara</v>
+      </c>
+    </row>
+    <row r="104" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" s="35" t="s">
         <v>207</v>
       </c>
-      <c r="E104" s="43"/>
-      <c r="F104" s="43"/>
-      <c r="G104" s="43"/>
-      <c r="H104" s="43"/>
-      <c r="I104" s="43"/>
-      <c r="J104" s="43"/>
-      <c r="K104" s="43"/>
-      <c r="L104" s="43"/>
+      <c r="B104" t="s">
+        <v>8</v>
+      </c>
+      <c r="C104">
+        <v>27</v>
+      </c>
+      <c r="D104" t="s">
+        <v>111</v>
+      </c>
+      <c r="E104" s="43">
+        <v>26500</v>
+      </c>
+      <c r="F104" s="43">
+        <v>3500</v>
+      </c>
+      <c r="G104" s="43">
+        <v>2500</v>
+      </c>
+      <c r="H104" s="43">
+        <v>2500</v>
+      </c>
+      <c r="I104" s="43">
+        <v>24840</v>
+      </c>
+      <c r="J104" s="43">
+        <v>10000</v>
+      </c>
+      <c r="K104" s="43">
+        <v>1000</v>
+      </c>
+      <c r="L104" s="43">
+        <v>14744.48</v>
+      </c>
       <c r="M104" s="44">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>85584.48</v>
       </c>
       <c r="N104" s="44">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="O104" s="43"/>
-      <c r="P104" s="43"/>
-      <c r="Q104" s="43"/>
-      <c r="R104" s="43"/>
-      <c r="S104" s="43"/>
-      <c r="T104" s="43"/>
-      <c r="U104" s="43"/>
+        <v>2400</v>
+      </c>
+      <c r="O104" s="43">
+        <v>12850</v>
+      </c>
+      <c r="P104" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q104" s="43">
+        <v>10000</v>
+      </c>
+      <c r="R104" s="43">
+        <v>2100</v>
+      </c>
+      <c r="S104" s="43">
+        <v>0</v>
+      </c>
+      <c r="T104" s="43">
+        <v>14744.48</v>
+      </c>
+      <c r="U104" s="43">
+        <v>0</v>
+      </c>
       <c r="V104" s="44">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>42094.479999999996</v>
       </c>
       <c r="W104" s="44">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>43490</v>
       </c>
       <c r="X104" s="44">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="Y104" s="44">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="Z104" s="50"/>
       <c r="AA104" s="47" t="str">
         <f t="shared" si="27"/>
-        <v>October 2026</v>
-      </c>
-    </row>
-    <row r="105" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>October 2026D M T S Disanayake</v>
+      </c>
+    </row>
+    <row r="105" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="35" t="s">
         <v>207</v>
       </c>
-      <c r="E105" s="43"/>
-      <c r="F105" s="43"/>
-      <c r="G105" s="43"/>
-      <c r="H105" s="43"/>
-      <c r="I105" s="43"/>
-      <c r="J105" s="43"/>
-      <c r="K105" s="43"/>
-      <c r="L105" s="43"/>
+      <c r="B105" t="s">
+        <v>141</v>
+      </c>
+      <c r="C105">
+        <v>28</v>
+      </c>
+      <c r="D105" t="s">
+        <v>86</v>
+      </c>
+      <c r="E105" s="43">
+        <v>36500</v>
+      </c>
+      <c r="F105" s="43">
+        <v>3500</v>
+      </c>
+      <c r="G105" s="43">
+        <v>10000</v>
+      </c>
+      <c r="H105" s="43">
+        <v>5000</v>
+      </c>
+      <c r="I105" s="43">
+        <v>26910</v>
+      </c>
+      <c r="J105" s="43">
+        <v>10000</v>
+      </c>
+      <c r="K105" s="43">
+        <v>1000</v>
+      </c>
+      <c r="L105" s="43">
+        <v>13958.68</v>
+      </c>
       <c r="M105" s="44">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>106868.68</v>
       </c>
       <c r="N105" s="44">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="O105" s="43"/>
-      <c r="P105" s="43"/>
-      <c r="Q105" s="43"/>
-      <c r="R105" s="43"/>
-      <c r="S105" s="43"/>
-      <c r="T105" s="43"/>
-      <c r="U105" s="43"/>
+        <v>3200</v>
+      </c>
+      <c r="O105" s="43">
+        <v>11850</v>
+      </c>
+      <c r="P105" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q105" s="43">
+        <v>10000</v>
+      </c>
+      <c r="R105" s="43">
+        <v>1500</v>
+      </c>
+      <c r="S105" s="43">
+        <v>0</v>
+      </c>
+      <c r="T105" s="43">
+        <v>13958.68</v>
+      </c>
+      <c r="U105" s="43">
+        <v>0</v>
+      </c>
       <c r="V105" s="44">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>40508.68</v>
       </c>
       <c r="W105" s="44">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>66360</v>
       </c>
       <c r="X105" s="44">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="Y105" s="44">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="Z105" s="50"/>
       <c r="AA105" s="47" t="str">
         <f t="shared" si="27"/>
-        <v>October 2026</v>
-      </c>
-    </row>
-    <row r="106" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>October 2026P L D B Wijewardhna</v>
+      </c>
+    </row>
+    <row r="106" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A106" s="35" t="s">
         <v>207</v>
       </c>
-      <c r="E106" s="43"/>
-      <c r="F106" s="43"/>
-      <c r="G106" s="43"/>
-      <c r="H106" s="43"/>
-      <c r="I106" s="43"/>
-      <c r="J106" s="43"/>
-      <c r="K106" s="43"/>
-      <c r="L106" s="43"/>
+      <c r="B106" t="s">
+        <v>146</v>
+      </c>
+      <c r="C106">
+        <v>29</v>
+      </c>
+      <c r="D106" t="s">
+        <v>111</v>
+      </c>
+      <c r="E106" s="43">
+        <v>26500</v>
+      </c>
+      <c r="F106" s="43">
+        <v>3500</v>
+      </c>
+      <c r="G106" s="43">
+        <v>5000</v>
+      </c>
+      <c r="H106" s="43">
+        <v>5000</v>
+      </c>
+      <c r="I106" s="43">
+        <v>18630</v>
+      </c>
+      <c r="J106" s="43">
+        <v>0</v>
+      </c>
+      <c r="K106" s="43">
+        <v>1000</v>
+      </c>
+      <c r="L106" s="43">
+        <v>2131.12</v>
+      </c>
       <c r="M106" s="44">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>61761.120000000003</v>
       </c>
       <c r="N106" s="44">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="O106" s="43"/>
-      <c r="P106" s="43"/>
-      <c r="Q106" s="43"/>
-      <c r="R106" s="43"/>
-      <c r="S106" s="43"/>
-      <c r="T106" s="43"/>
-      <c r="U106" s="43"/>
+        <v>2400</v>
+      </c>
+      <c r="O106" s="43">
+        <v>15850</v>
+      </c>
+      <c r="P106" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q106" s="43">
+        <v>0</v>
+      </c>
+      <c r="R106" s="43">
+        <v>0</v>
+      </c>
+      <c r="S106" s="43">
+        <v>0</v>
+      </c>
+      <c r="T106" s="43">
+        <v>2131.12</v>
+      </c>
+      <c r="U106" s="43">
+        <v>0</v>
+      </c>
       <c r="V106" s="44">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>20381.12</v>
       </c>
       <c r="W106" s="44">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>41380</v>
       </c>
       <c r="X106" s="44">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="Y106" s="44">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="Z106" s="50"/>
       <c r="AA106" s="47" t="str">
         <f t="shared" si="27"/>
-        <v>October 2026</v>
-      </c>
-    </row>
-    <row r="107" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>October 2026N G L D Supunsiri</v>
+      </c>
+    </row>
+    <row r="107" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" s="35" t="s">
         <v>208</v>
       </c>
@@ -12018,7 +12616,7 @@
         <v>November 2026</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A108" s="35" t="s">
         <v>208</v>
       </c>
@@ -12067,7 +12665,7 @@
         <v>November 2026</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" s="35" t="s">
         <v>208</v>
       </c>
@@ -12116,7 +12714,7 @@
         <v>November 2026</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A110" s="35" t="s">
         <v>208</v>
       </c>
@@ -12165,7 +12763,7 @@
         <v>November 2026</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A111" s="35" t="s">
         <v>208</v>
       </c>
@@ -12214,7 +12812,7 @@
         <v>November 2026</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A112" s="35" t="s">
         <v>208</v>
       </c>
@@ -12263,7 +12861,7 @@
         <v>November 2026</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A113" s="35" t="s">
         <v>208</v>
       </c>
@@ -12312,7 +12910,7 @@
         <v>November 2026</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A114" s="35" t="s">
         <v>208</v>
       </c>
@@ -12361,7 +12959,7 @@
         <v>November 2026</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A115" s="35" t="s">
         <v>208</v>
       </c>
@@ -12410,7 +13008,7 @@
         <v>November 2026</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A116" s="35" t="s">
         <v>208</v>
       </c>
@@ -12459,7 +13057,7 @@
         <v>November 2026</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="35" t="s">
         <v>208</v>
       </c>
@@ -12508,7 +13106,7 @@
         <v>November 2026</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A118" s="35" t="s">
         <v>208</v>
       </c>
@@ -12557,7 +13155,7 @@
         <v>November 2026</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A119" s="35" t="s">
         <v>208</v>
       </c>
@@ -12606,7 +13204,7 @@
         <v>November 2026</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A120" s="35" t="s">
         <v>208</v>
       </c>
@@ -12655,7 +13253,7 @@
         <v>November 2026</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A121" s="35" t="s">
         <v>208</v>
       </c>
@@ -12704,7 +13302,7 @@
         <v>November 2026</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" s="35" t="s">
         <v>209</v>
       </c>
@@ -12753,7 +13351,7 @@
         <v>December 2026</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A123" s="35" t="s">
         <v>209</v>
       </c>
@@ -12802,7 +13400,7 @@
         <v>December 2026</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A124" s="35" t="s">
         <v>209</v>
       </c>
@@ -12851,7 +13449,7 @@
         <v>December 2026</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A125" s="35" t="s">
         <v>209</v>
       </c>
@@ -12900,7 +13498,7 @@
         <v>December 2026</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="35" t="s">
         <v>209</v>
       </c>
@@ -12949,7 +13547,7 @@
         <v>December 2026</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A127" s="35" t="s">
         <v>209</v>
       </c>
@@ -12998,7 +13596,7 @@
         <v>December 2026</v>
       </c>
     </row>
-    <row r="128" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A128" s="35" t="s">
         <v>209</v>
       </c>
@@ -13047,7 +13645,7 @@
         <v>December 2026</v>
       </c>
     </row>
-    <row r="129" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A129" s="35" t="s">
         <v>209</v>
       </c>
@@ -13096,7 +13694,7 @@
         <v>December 2026</v>
       </c>
     </row>
-    <row r="130" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A130" s="35" t="s">
         <v>209</v>
       </c>
@@ -13145,7 +13743,7 @@
         <v>December 2026</v>
       </c>
     </row>
-    <row r="131" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="35" t="s">
         <v>209</v>
       </c>
@@ -13194,7 +13792,7 @@
         <v>December 2026</v>
       </c>
     </row>
-    <row r="132" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A132" s="35" t="s">
         <v>209</v>
       </c>
@@ -13243,7 +13841,7 @@
         <v>December 2026</v>
       </c>
     </row>
-    <row r="133" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A133" s="35" t="s">
         <v>209</v>
       </c>
@@ -13292,7 +13890,7 @@
         <v>December 2026</v>
       </c>
     </row>
-    <row r="134" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A134" s="35" t="s">
         <v>209</v>
       </c>
@@ -13341,7 +13939,7 @@
         <v>December 2026</v>
       </c>
     </row>
-    <row r="135" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" s="35" t="s">
         <v>209</v>
       </c>
@@ -13390,7 +13988,7 @@
         <v>December 2026</v>
       </c>
     </row>
-    <row r="136" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A136" s="35" t="s">
         <v>209</v>
       </c>
@@ -13439,7 +14037,7 @@
         <v>December 2026</v>
       </c>
     </row>
-    <row r="137" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A137" s="35" t="s">
         <v>210</v>
       </c>
@@ -13488,7 +14086,7 @@
         <v>January 2027</v>
       </c>
     </row>
-    <row r="138" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A138" s="35" t="s">
         <v>210</v>
       </c>
@@ -13537,7 +14135,7 @@
         <v>January 2027</v>
       </c>
     </row>
-    <row r="139" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A139" s="35" t="s">
         <v>210</v>
       </c>
@@ -13586,7 +14184,7 @@
         <v>January 2027</v>
       </c>
     </row>
-    <row r="140" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A140" s="35" t="s">
         <v>210</v>
       </c>
@@ -13635,7 +14233,7 @@
         <v>January 2027</v>
       </c>
     </row>
-    <row r="141" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A141" s="35" t="s">
         <v>210</v>
       </c>
@@ -13684,7 +14282,7 @@
         <v>January 2027</v>
       </c>
     </row>
-    <row r="142" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A142" s="35" t="s">
         <v>210</v>
       </c>
@@ -13733,7 +14331,7 @@
         <v>January 2027</v>
       </c>
     </row>
-    <row r="143" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A143" s="35" t="s">
         <v>210</v>
       </c>
@@ -13782,7 +14380,7 @@
         <v>January 2027</v>
       </c>
     </row>
-    <row r="144" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A144" s="35" t="s">
         <v>210</v>
       </c>
@@ -13831,7 +14429,7 @@
         <v>January 2027</v>
       </c>
     </row>
-    <row r="145" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A145" s="35" t="s">
         <v>210</v>
       </c>
@@ -13880,7 +14478,7 @@
         <v>January 2027</v>
       </c>
     </row>
-    <row r="146" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A146" s="35" t="s">
         <v>210</v>
       </c>
@@ -13929,7 +14527,7 @@
         <v>January 2027</v>
       </c>
     </row>
-    <row r="147" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A147" s="35" t="s">
         <v>210</v>
       </c>
@@ -13978,7 +14576,7 @@
         <v>January 2027</v>
       </c>
     </row>
-    <row r="148" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A148" s="35" t="s">
         <v>210</v>
       </c>
@@ -14027,7 +14625,7 @@
         <v>January 2027</v>
       </c>
     </row>
-    <row r="149" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" s="35" t="s">
         <v>210</v>
       </c>
@@ -14076,7 +14674,7 @@
         <v>January 2027</v>
       </c>
     </row>
-    <row r="150" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A150" s="35" t="s">
         <v>210</v>
       </c>
@@ -14125,7 +14723,7 @@
         <v>January 2027</v>
       </c>
     </row>
-    <row r="151" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A151" s="35" t="s">
         <v>210</v>
       </c>
@@ -14174,7 +14772,7 @@
         <v>January 2027</v>
       </c>
     </row>
-    <row r="152" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A152" s="35" t="s">
         <v>211</v>
       </c>
@@ -14223,7 +14821,7 @@
         <v>February 2027</v>
       </c>
     </row>
-    <row r="153" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A153" s="35" t="s">
         <v>211</v>
       </c>
@@ -14272,7 +14870,7 @@
         <v>February 2027</v>
       </c>
     </row>
-    <row r="154" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A154" s="35" t="s">
         <v>211</v>
       </c>
@@ -14321,7 +14919,7 @@
         <v>February 2027</v>
       </c>
     </row>
-    <row r="155" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A155" s="35" t="s">
         <v>211</v>
       </c>
@@ -14370,7 +14968,7 @@
         <v>February 2027</v>
       </c>
     </row>
-    <row r="156" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A156" s="35" t="s">
         <v>211</v>
       </c>
@@ -14419,7 +15017,7 @@
         <v>February 2027</v>
       </c>
     </row>
-    <row r="157" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A157" s="35" t="s">
         <v>211</v>
       </c>
@@ -14468,7 +15066,7 @@
         <v>February 2027</v>
       </c>
     </row>
-    <row r="158" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A158" s="35" t="s">
         <v>211</v>
       </c>
@@ -14517,7 +15115,7 @@
         <v>February 2027</v>
       </c>
     </row>
-    <row r="159" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A159" s="35" t="s">
         <v>211</v>
       </c>
@@ -14566,7 +15164,7 @@
         <v>February 2027</v>
       </c>
     </row>
-    <row r="160" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A160" s="35" t="s">
         <v>211</v>
       </c>
@@ -14615,7 +15213,7 @@
         <v>February 2027</v>
       </c>
     </row>
-    <row r="161" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A161" s="35" t="s">
         <v>211</v>
       </c>
@@ -14664,7 +15262,7 @@
         <v>February 2027</v>
       </c>
     </row>
-    <row r="162" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A162" s="35" t="s">
         <v>211</v>
       </c>
@@ -14713,7 +15311,7 @@
         <v>February 2027</v>
       </c>
     </row>
-    <row r="163" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A163" s="35" t="s">
         <v>211</v>
       </c>
@@ -14762,7 +15360,7 @@
         <v>February 2027</v>
       </c>
     </row>
-    <row r="164" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A164" s="35" t="s">
         <v>211</v>
       </c>
@@ -14811,7 +15409,7 @@
         <v>February 2027</v>
       </c>
     </row>
-    <row r="165" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A165" s="35" t="s">
         <v>211</v>
       </c>
@@ -14860,7 +15458,7 @@
         <v>February 2027</v>
       </c>
     </row>
-    <row r="166" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A166" s="35" t="s">
         <v>211</v>
       </c>
@@ -14909,7 +15507,7 @@
         <v>February 2027</v>
       </c>
     </row>
-    <row r="167" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A167" s="35" t="s">
         <v>212</v>
       </c>
@@ -14958,7 +15556,7 @@
         <v>March 2027</v>
       </c>
     </row>
-    <row r="168" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A168" s="35" t="s">
         <v>212</v>
       </c>
@@ -15007,7 +15605,7 @@
         <v>March 2027</v>
       </c>
     </row>
-    <row r="169" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A169" s="35" t="s">
         <v>212</v>
       </c>
@@ -15056,7 +15654,7 @@
         <v>March 2027</v>
       </c>
     </row>
-    <row r="170" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" s="35" t="s">
         <v>212</v>
       </c>
@@ -15105,7 +15703,7 @@
         <v>March 2027</v>
       </c>
     </row>
-    <row r="171" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A171" s="35" t="s">
         <v>212</v>
       </c>
@@ -15154,7 +15752,7 @@
         <v>March 2027</v>
       </c>
     </row>
-    <row r="172" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A172" s="35" t="s">
         <v>212</v>
       </c>
@@ -15203,7 +15801,7 @@
         <v>March 2027</v>
       </c>
     </row>
-    <row r="173" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A173" s="35" t="s">
         <v>212</v>
       </c>
@@ -15252,7 +15850,7 @@
         <v>March 2027</v>
       </c>
     </row>
-    <row r="174" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A174" s="35" t="s">
         <v>212</v>
       </c>
@@ -15301,7 +15899,7 @@
         <v>March 2027</v>
       </c>
     </row>
-    <row r="175" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A175" s="35" t="s">
         <v>212</v>
       </c>
@@ -15350,7 +15948,7 @@
         <v>March 2027</v>
       </c>
     </row>
-    <row r="176" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A176" s="35" t="s">
         <v>212</v>
       </c>
@@ -15399,7 +15997,7 @@
         <v>March 2027</v>
       </c>
     </row>
-    <row r="177" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A177" s="35" t="s">
         <v>212</v>
       </c>
@@ -15448,7 +16046,7 @@
         <v>March 2027</v>
       </c>
     </row>
-    <row r="178" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A178" s="35" t="s">
         <v>212</v>
       </c>
@@ -15497,7 +16095,7 @@
         <v>March 2027</v>
       </c>
     </row>
-    <row r="179" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A179" s="35" t="s">
         <v>212</v>
       </c>
@@ -15546,7 +16144,7 @@
         <v>March 2027</v>
       </c>
     </row>
-    <row r="180" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A180" s="35" t="s">
         <v>212</v>
       </c>
@@ -15595,7 +16193,7 @@
         <v>March 2027</v>
       </c>
     </row>
-    <row r="181" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:27" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A181" s="35" t="s">
         <v>212</v>
       </c>
@@ -15644,7 +16242,7 @@
         <v>March 2027</v>
       </c>
     </row>
-    <row r="182" spans="1:27" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="182" spans="1:27" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <autoFilter ref="A1:Y181" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
